--- a/dashboard_output_SDG10.xlsx
+++ b/dashboard_output_SDG10.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Q172"/>
+  <dimension ref="A1:P172"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -387,57 +387,52 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
+          <t>reach_target_year</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
           <t>speed</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>pctl</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>end_year</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>end_value</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>start_value</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>indicator_sdg</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>indicatorname</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>start_year</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>end_year</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>end_value</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>typical_end_value</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>indicator_sdg</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>indicatorname</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>start_value</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>reach_target_year</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>reach_target</t>
         </is>
       </c>
     </row>
@@ -509,15 +504,15 @@
         </is>
       </c>
       <c r="G3">
-        <v>1.25</v>
-      </c>
-      <c r="H3" t="inlineStr">
+        <v>2059</v>
+      </c>
+      <c r="H3">
+        <v>1.476190476190476</v>
+      </c>
+      <c r="I3" t="inlineStr">
         <is>
           <t>40-60</t>
         </is>
-      </c>
-      <c r="I3">
-        <v>2015</v>
       </c>
       <c r="J3">
         <v>2020</v>
@@ -526,7 +521,7 @@
         <v>2.5</v>
       </c>
       <c r="L3">
-        <v>1.589285714285708</v>
+        <v>3</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -539,15 +534,10 @@
         </is>
       </c>
       <c r="O3">
-        <v>3</v>
+        <v>2015</v>
       </c>
       <c r="P3">
-        <v>2056</v>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>future</t>
-        </is>
+        <v>2.65</v>
       </c>
     </row>
     <row r="4">
@@ -575,6 +565,9 @@
           <t>ARE</t>
         </is>
       </c>
+      <c r="G4">
+        <v>2018</v>
+      </c>
       <c r="J4">
         <v>2018</v>
       </c>
@@ -591,14 +584,6 @@
           <t>Prosperity gap (average shortfall from a prosperity standard of $25/day)</t>
         </is>
       </c>
-      <c r="P4">
-        <v>2018</v>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>past</t>
-        </is>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -625,38 +610,33 @@
           <t>ARG</t>
         </is>
       </c>
-      <c r="G5">
-        <v>-0.816326530612244</v>
-      </c>
-      <c r="I5">
+      <c r="H5">
+        <v>-0.5</v>
+      </c>
+      <c r="J5">
+        <v>2024</v>
+      </c>
+      <c r="K5">
+        <v>2.1</v>
+      </c>
+      <c r="L5">
+        <v>1.9</v>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>10.1.1</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>Prosperity gap (average shortfall from a prosperity standard of $25/day)</t>
+        </is>
+      </c>
+      <c r="O5">
         <v>2016</v>
       </c>
-      <c r="J5">
-        <v>2023</v>
-      </c>
-      <c r="K5">
-        <v>2.3</v>
-      </c>
-      <c r="L5">
-        <v>0.6766666666666606</v>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>10.1.1</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>Prosperity gap (average shortfall from a prosperity standard of $25/day)</t>
-        </is>
-      </c>
-      <c r="O5">
-        <v>1.9</v>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>never</t>
-        </is>
+      <c r="P5">
+        <v>1.54</v>
       </c>
     </row>
     <row r="6">
@@ -684,16 +664,13 @@
           <t>ARM</t>
         </is>
       </c>
-      <c r="G6">
-        <v>-0.15625</v>
-      </c>
-      <c r="H6" t="inlineStr">
+      <c r="H6">
+        <v>-0.125</v>
+      </c>
+      <c r="I6" t="inlineStr">
         <is>
           <t>0-20</t>
         </is>
-      </c>
-      <c r="I6">
-        <v>2015</v>
       </c>
       <c r="J6">
         <v>2023</v>
@@ -702,7 +679,7 @@
         <v>4</v>
       </c>
       <c r="L6">
-        <v>1.544285714285717</v>
+        <v>3.9</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -715,12 +692,10 @@
         </is>
       </c>
       <c r="O6">
-        <v>3.9</v>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>never</t>
-        </is>
+        <v>2015</v>
+      </c>
+      <c r="P6">
+        <v>3.195555555555547</v>
       </c>
     </row>
     <row r="7">
@@ -749,10 +724,10 @@
         </is>
       </c>
       <c r="J7">
-        <v>2018</v>
+        <v>2020</v>
       </c>
       <c r="K7">
-        <v>0.9</v>
+        <v>1.1</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -791,45 +766,40 @@
         </is>
       </c>
       <c r="G8">
-        <v>2.380952380952382</v>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>80-100</t>
-        </is>
-      </c>
-      <c r="I8">
+        <v>2033</v>
+      </c>
+      <c r="H8">
+        <v>1.458333333333334</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>60-80</t>
+        </is>
+      </c>
+      <c r="J8">
+        <v>2023</v>
+      </c>
+      <c r="K8">
+        <v>0.8</v>
+      </c>
+      <c r="L8">
+        <v>1.1</v>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>10.1.1</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>Prosperity gap (average shortfall from a prosperity standard of $25/day)</t>
+        </is>
+      </c>
+      <c r="O8">
         <v>2015</v>
       </c>
-      <c r="J8">
-        <v>2022</v>
-      </c>
-      <c r="K8">
-        <v>0.6000000000000001</v>
-      </c>
-      <c r="L8">
-        <v>0.3866666666666697</v>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>10.1.1</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>Prosperity gap (average shortfall from a prosperity standard of $25/day)</t>
-        </is>
-      </c>
-      <c r="O8">
-        <v>1.1</v>
-      </c>
       <c r="P8">
-        <v>2024</v>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>future</t>
-        </is>
+        <v>0.8733333333333348</v>
       </c>
     </row>
     <row r="9">
@@ -942,45 +912,40 @@
         </is>
       </c>
       <c r="G11">
-        <v>0.7142857142857143</v>
-      </c>
-      <c r="H11" t="inlineStr">
+        <v>2020</v>
+      </c>
+      <c r="H11">
+        <v>0.625</v>
+      </c>
+      <c r="I11" t="inlineStr">
         <is>
           <t>80-100</t>
         </is>
       </c>
-      <c r="I11">
+      <c r="J11">
+        <v>2023</v>
+      </c>
+      <c r="K11">
+        <v>0.5</v>
+      </c>
+      <c r="L11">
+        <v>0.6000000000000001</v>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>10.1.1</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>Prosperity gap (average shortfall from a prosperity standard of $25/day)</t>
+        </is>
+      </c>
+      <c r="O11">
         <v>2015</v>
       </c>
-      <c r="J11">
-        <v>2022</v>
-      </c>
-      <c r="K11">
-        <v>0.5</v>
-      </c>
-      <c r="L11">
-        <v>0.22</v>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>10.1.1</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>Prosperity gap (average shortfall from a prosperity standard of $25/day)</t>
-        </is>
-      </c>
-      <c r="O11">
-        <v>0.6000000000000001</v>
-      </c>
       <c r="P11">
-        <v>2020</v>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>past</t>
-        </is>
+        <v>0.44</v>
       </c>
     </row>
     <row r="12">
@@ -1009,15 +974,15 @@
         </is>
       </c>
       <c r="G12">
-        <v>1.948278670059259</v>
-      </c>
-      <c r="H12" t="inlineStr">
+        <v>2037</v>
+      </c>
+      <c r="H12">
+        <v>6.578328682917953</v>
+      </c>
+      <c r="I12" t="inlineStr">
         <is>
           <t>80-100</t>
         </is>
-      </c>
-      <c r="I12">
-        <v>2015</v>
       </c>
       <c r="J12">
         <v>2021</v>
@@ -1026,7 +991,7 @@
         <v>7.7</v>
       </c>
       <c r="L12">
-        <v>6.43930962576429</v>
+        <v>21.5</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -1039,15 +1004,10 @@
         </is>
       </c>
       <c r="O12">
-        <v>21.5</v>
+        <v>2015</v>
       </c>
       <c r="P12">
-        <v>2078</v>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>future</t>
-        </is>
+        <v>18.21696157739227</v>
       </c>
     </row>
     <row r="13">
@@ -1118,19 +1078,19 @@
         </is>
       </c>
       <c r="G14">
-        <v>3.584656084656085</v>
-      </c>
-      <c r="I14">
-        <v>2016</v>
+        <v>2064</v>
+      </c>
+      <c r="H14">
+        <v>2.04620053149465</v>
       </c>
       <c r="J14">
         <v>2022</v>
       </c>
       <c r="K14">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="L14">
-        <v>5.025555555555563</v>
+        <v>6.800000000000001</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -1143,15 +1103,10 @@
         </is>
       </c>
       <c r="O14">
-        <v>6.800000000000001</v>
+        <v>2016</v>
       </c>
       <c r="P14">
-        <v>2045</v>
-      </c>
-      <c r="Q14" t="inlineStr">
-        <is>
-          <t>future</t>
-        </is>
+        <v>5.851470588235293</v>
       </c>
     </row>
     <row r="15">
@@ -1180,45 +1135,40 @@
         </is>
       </c>
       <c r="G15">
-        <v>3.069727891156463</v>
-      </c>
-      <c r="H15" t="inlineStr">
+        <v>2033</v>
+      </c>
+      <c r="H15">
+        <v>3.693452380952381</v>
+      </c>
+      <c r="I15" t="inlineStr">
         <is>
           <t>80-100</t>
         </is>
       </c>
-      <c r="I15">
+      <c r="J15">
+        <v>2023</v>
+      </c>
+      <c r="K15">
+        <v>1.4</v>
+      </c>
+      <c r="L15">
+        <v>3</v>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>10.1.1</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>Prosperity gap (average shortfall from a prosperity standard of $25/day)</t>
+        </is>
+      </c>
+      <c r="O15">
         <v>2015</v>
       </c>
-      <c r="J15">
-        <v>2022</v>
-      </c>
-      <c r="K15">
-        <v>1.5</v>
-      </c>
-      <c r="L15">
-        <v>1.179523809523817</v>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>10.1.1</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>Prosperity gap (average shortfall from a prosperity standard of $25/day)</t>
-        </is>
-      </c>
-      <c r="O15">
-        <v>3</v>
-      </c>
       <c r="P15">
-        <v>2032</v>
-      </c>
-      <c r="Q15" t="inlineStr">
-        <is>
-          <t>future</t>
-        </is>
+        <v>2.46285714285714</v>
       </c>
     </row>
     <row r="16">
@@ -1289,15 +1239,15 @@
         </is>
       </c>
       <c r="G17">
-        <v>1</v>
-      </c>
-      <c r="H17" t="inlineStr">
+        <v>2051</v>
+      </c>
+      <c r="H17">
+        <v>1.3</v>
+      </c>
+      <c r="I17" t="inlineStr">
         <is>
           <t>40-60</t>
         </is>
-      </c>
-      <c r="I17">
-        <v>2015</v>
       </c>
       <c r="J17">
         <v>2020</v>
@@ -1306,7 +1256,7 @@
         <v>1.6</v>
       </c>
       <c r="L17">
-        <v>0.9066666666666788</v>
+        <v>1.9</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -1319,15 +1269,10 @@
         </is>
       </c>
       <c r="O17">
-        <v>1.9</v>
+        <v>2015</v>
       </c>
       <c r="P17">
-        <v>2052</v>
-      </c>
-      <c r="Q17" t="inlineStr">
-        <is>
-          <t>future</t>
-        </is>
+        <v>1.66</v>
       </c>
     </row>
     <row r="18">
@@ -1398,15 +1343,15 @@
         </is>
       </c>
       <c r="G19">
-        <v>1.897321428571429</v>
-      </c>
-      <c r="H19" t="inlineStr">
+        <v>2051</v>
+      </c>
+      <c r="H19">
+        <v>2.03373015873016</v>
+      </c>
+      <c r="I19" t="inlineStr">
         <is>
           <t>80-100</t>
         </is>
-      </c>
-      <c r="I19">
-        <v>2015</v>
       </c>
       <c r="J19">
         <v>2023</v>
@@ -1415,7 +1360,7 @@
         <v>2.4</v>
       </c>
       <c r="L19">
-        <v>1.349404761904771</v>
+        <v>3.6</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -1428,15 +1373,10 @@
         </is>
       </c>
       <c r="O19">
-        <v>3.6</v>
+        <v>2015</v>
       </c>
       <c r="P19">
-        <v>2046</v>
-      </c>
-      <c r="Q19" t="inlineStr">
-        <is>
-          <t>future</t>
-        </is>
+        <v>2.945555555555557</v>
       </c>
     </row>
     <row r="20">
@@ -1465,15 +1405,15 @@
         </is>
       </c>
       <c r="G20">
+        <v>2162</v>
+      </c>
+      <c r="H20">
         <v>0.46875</v>
       </c>
-      <c r="H20" t="inlineStr">
+      <c r="I20" t="inlineStr">
         <is>
           <t>20-40</t>
         </is>
-      </c>
-      <c r="I20">
-        <v>2015</v>
       </c>
       <c r="J20">
         <v>2023</v>
@@ -1482,7 +1422,7 @@
         <v>3</v>
       </c>
       <c r="L20">
-        <v>1.169523809523817</v>
+        <v>3.3</v>
       </c>
       <c r="M20" t="inlineStr">
         <is>
@@ -1495,15 +1435,10 @@
         </is>
       </c>
       <c r="O20">
-        <v>3.3</v>
+        <v>2015</v>
       </c>
       <c r="P20">
-        <v>2133</v>
-      </c>
-      <c r="Q20" t="inlineStr">
-        <is>
-          <t>future</t>
-        </is>
+        <v>2.702499999999996</v>
       </c>
     </row>
     <row r="21">
@@ -1574,10 +1509,10 @@
         </is>
       </c>
       <c r="G22">
-        <v>3.928571428571428</v>
-      </c>
-      <c r="I22">
-        <v>2017</v>
+        <v>2033</v>
+      </c>
+      <c r="H22">
+        <v>4.431746031746033</v>
       </c>
       <c r="J22">
         <v>2022</v>
@@ -1586,7 +1521,7 @@
         <v>2</v>
       </c>
       <c r="L22">
-        <v>1.974999999999984</v>
+        <v>3.5</v>
       </c>
       <c r="M22" t="inlineStr">
         <is>
@@ -1599,15 +1534,10 @@
         </is>
       </c>
       <c r="O22">
-        <v>3.5</v>
+        <v>2017</v>
       </c>
       <c r="P22">
-        <v>2032</v>
-      </c>
-      <c r="Q22" t="inlineStr">
-        <is>
-          <t>future</t>
-        </is>
+        <v>3.088888888888887</v>
       </c>
     </row>
     <row r="23">
@@ -1720,45 +1650,40 @@
         </is>
       </c>
       <c r="G25">
-        <v>2</v>
-      </c>
-      <c r="H25" t="inlineStr">
+        <v>2020</v>
+      </c>
+      <c r="H25">
+        <v>1.666666666666667</v>
+      </c>
+      <c r="I25" t="inlineStr">
         <is>
           <t>80-100</t>
         </is>
       </c>
-      <c r="I25">
+      <c r="J25">
+        <v>2021</v>
+      </c>
+      <c r="K25">
+        <v>0.5</v>
+      </c>
+      <c r="L25">
+        <v>0.7000000000000001</v>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>10.1.1</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>Prosperity gap (average shortfall from a prosperity standard of $25/day)</t>
+        </is>
+      </c>
+      <c r="O25">
         <v>2015</v>
       </c>
-      <c r="J25">
-        <v>2020</v>
-      </c>
-      <c r="K25">
-        <v>0.5</v>
-      </c>
-      <c r="L25">
-        <v>0.35</v>
-      </c>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>10.1.1</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>Prosperity gap (average shortfall from a prosperity standard of $25/day)</t>
-        </is>
-      </c>
-      <c r="O25">
-        <v>0.7000000000000001</v>
-      </c>
       <c r="P25">
-        <v>2020</v>
-      </c>
-      <c r="Q25" t="inlineStr">
-        <is>
-          <t>past</t>
-        </is>
+        <v>0.5800000000000001</v>
       </c>
     </row>
     <row r="26">
@@ -1787,45 +1712,40 @@
         </is>
       </c>
       <c r="G26">
-        <v>0</v>
-      </c>
-      <c r="H26" t="inlineStr">
+        <v>2007</v>
+      </c>
+      <c r="H26">
+        <v>0</v>
+      </c>
+      <c r="I26" t="inlineStr">
         <is>
           <t>0-20</t>
         </is>
       </c>
-      <c r="I26">
+      <c r="J26">
+        <v>2022</v>
+      </c>
+      <c r="K26">
+        <v>0.5</v>
+      </c>
+      <c r="L26">
+        <v>0.5</v>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>10.1.1</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>Prosperity gap (average shortfall from a prosperity standard of $25/day)</t>
+        </is>
+      </c>
+      <c r="O26">
         <v>2015</v>
       </c>
-      <c r="J26">
-        <v>2021</v>
-      </c>
-      <c r="K26">
-        <v>0.5</v>
-      </c>
-      <c r="L26">
-        <v>0.21</v>
-      </c>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>10.1.1</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>Prosperity gap (average shortfall from a prosperity standard of $25/day)</t>
-        </is>
-      </c>
-      <c r="O26">
-        <v>0.5</v>
-      </c>
       <c r="P26">
-        <v>2007</v>
-      </c>
-      <c r="Q26" t="inlineStr">
-        <is>
-          <t>past</t>
-        </is>
+        <v>0.38</v>
       </c>
     </row>
     <row r="27">
@@ -1854,15 +1774,15 @@
         </is>
       </c>
       <c r="G27">
-        <v>0.6802721088435391</v>
-      </c>
-      <c r="H27" t="inlineStr">
+        <v>2073</v>
+      </c>
+      <c r="H27">
+        <v>0.8571428571428571</v>
+      </c>
+      <c r="I27" t="inlineStr">
         <is>
           <t>40-60</t>
         </is>
-      </c>
-      <c r="I27">
-        <v>2015</v>
       </c>
       <c r="J27">
         <v>2022</v>
@@ -1871,7 +1791,7 @@
         <v>1.7</v>
       </c>
       <c r="L27">
-        <v>0.7078571428571384</v>
+        <v>2</v>
       </c>
       <c r="M27" t="inlineStr">
         <is>
@@ -1884,15 +1804,10 @@
         </is>
       </c>
       <c r="O27">
-        <v>2</v>
+        <v>2015</v>
       </c>
       <c r="P27">
-        <v>2071</v>
-      </c>
-      <c r="Q27" t="inlineStr">
-        <is>
-          <t>future</t>
-        </is>
+        <v>1.66</v>
       </c>
     </row>
     <row r="28">
@@ -1921,24 +1836,24 @@
         </is>
       </c>
       <c r="G28">
-        <v>2.529761904761905</v>
-      </c>
-      <c r="H28" t="inlineStr">
+        <v>2046</v>
+      </c>
+      <c r="H28">
+        <v>2.324263038548754</v>
+      </c>
+      <c r="I28" t="inlineStr">
         <is>
           <t>80-100</t>
         </is>
       </c>
-      <c r="I28">
-        <v>2015</v>
-      </c>
       <c r="J28">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="K28">
         <v>2.4</v>
       </c>
       <c r="L28">
-        <v>1.799285714285724</v>
+        <v>3.6</v>
       </c>
       <c r="M28" t="inlineStr">
         <is>
@@ -1951,15 +1866,10 @@
         </is>
       </c>
       <c r="O28">
-        <v>3.6</v>
+        <v>2015</v>
       </c>
       <c r="P28">
-        <v>2038</v>
-      </c>
-      <c r="Q28" t="inlineStr">
-        <is>
-          <t>future</t>
-        </is>
+        <v>3.017777777777774</v>
       </c>
     </row>
     <row r="29">
@@ -1988,15 +1898,15 @@
         </is>
       </c>
       <c r="G29">
-        <v>3.804400704894197</v>
-      </c>
-      <c r="H29" t="inlineStr">
+        <v>2048</v>
+      </c>
+      <c r="H29">
+        <v>3.626845358523483</v>
+      </c>
+      <c r="I29" t="inlineStr">
         <is>
           <t>80-100</t>
         </is>
-      </c>
-      <c r="I29">
-        <v>2015</v>
       </c>
       <c r="J29">
         <v>2021</v>
@@ -2005,7 +1915,7 @@
         <v>6.7</v>
       </c>
       <c r="L29">
-        <v>6.595001227238099</v>
+        <v>11.6</v>
       </c>
       <c r="M29" t="inlineStr">
         <is>
@@ -2018,15 +1928,10 @@
         </is>
       </c>
       <c r="O29">
-        <v>11.6</v>
+        <v>2015</v>
       </c>
       <c r="P29">
-        <v>2048</v>
-      </c>
-      <c r="Q29" t="inlineStr">
-        <is>
-          <t>future</t>
-        </is>
+        <v>9.954082635117128</v>
       </c>
     </row>
     <row r="30">
@@ -2180,16 +2085,13 @@
           <t>COL</t>
         </is>
       </c>
-      <c r="G33">
-        <v>-0.1785714285714288</v>
-      </c>
-      <c r="H33" t="inlineStr">
+      <c r="H33">
+        <v>-0.1136363636363633</v>
+      </c>
+      <c r="I33" t="inlineStr">
         <is>
           <t>0-20</t>
         </is>
-      </c>
-      <c r="I33">
-        <v>2015</v>
       </c>
       <c r="J33">
         <v>2023</v>
@@ -2198,7 +2100,7 @@
         <v>4.600000000000001</v>
       </c>
       <c r="L33">
-        <v>2.034999999999997</v>
+        <v>4.5</v>
       </c>
       <c r="M33" t="inlineStr">
         <is>
@@ -2211,12 +2113,10 @@
         </is>
       </c>
       <c r="O33">
-        <v>4.5</v>
-      </c>
-      <c r="Q33" t="inlineStr">
-        <is>
-          <t>never</t>
-        </is>
+        <v>2015</v>
+      </c>
+      <c r="P33">
+        <v>3.685454545454545</v>
       </c>
     </row>
     <row r="34">
@@ -2329,45 +2229,40 @@
         </is>
       </c>
       <c r="G36">
-        <v>0.7142857142857135</v>
-      </c>
-      <c r="H36" t="inlineStr">
+        <v>2075</v>
+      </c>
+      <c r="H36">
+        <v>0.9629629629629635</v>
+      </c>
+      <c r="I36" t="inlineStr">
         <is>
           <t>40-60</t>
         </is>
       </c>
-      <c r="I36">
+      <c r="J36">
+        <v>2024</v>
+      </c>
+      <c r="K36">
+        <v>2</v>
+      </c>
+      <c r="L36">
+        <v>2.5</v>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>10.1.1</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>Prosperity gap (average shortfall from a prosperity standard of $25/day)</t>
+        </is>
+      </c>
+      <c r="O36">
         <v>2015</v>
       </c>
-      <c r="J36">
-        <v>2023</v>
-      </c>
-      <c r="K36">
-        <v>2.1</v>
-      </c>
-      <c r="L36">
-        <v>0.8021428571428535</v>
-      </c>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>10.1.1</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr">
-        <is>
-          <t>Prosperity gap (average shortfall from a prosperity standard of $25/day)</t>
-        </is>
-      </c>
-      <c r="O36">
-        <v>2.5</v>
-      </c>
       <c r="P36">
-        <v>2079</v>
-      </c>
-      <c r="Q36" t="inlineStr">
-        <is>
-          <t>future</t>
-        </is>
+        <v>1.983333333333337</v>
       </c>
     </row>
     <row r="37">
@@ -2396,24 +2291,24 @@
         </is>
       </c>
       <c r="G37">
-        <v>1.190476190476192</v>
-      </c>
-      <c r="H37" t="inlineStr">
+        <v>2027</v>
+      </c>
+      <c r="H37">
+        <v>1.25</v>
+      </c>
+      <c r="I37" t="inlineStr">
         <is>
           <t>80-100</t>
         </is>
       </c>
-      <c r="I37">
-        <v>2015</v>
-      </c>
       <c r="J37">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="K37">
         <v>0.6000000000000001</v>
       </c>
       <c r="L37">
-        <v>0.3033333333333303</v>
+        <v>0.8</v>
       </c>
       <c r="M37" t="inlineStr">
         <is>
@@ -2426,15 +2321,10 @@
         </is>
       </c>
       <c r="O37">
-        <v>0.8</v>
+        <v>2015</v>
       </c>
       <c r="P37">
-        <v>2026</v>
-      </c>
-      <c r="Q37" t="inlineStr">
-        <is>
-          <t>future</t>
-        </is>
+        <v>0.6400000000000001</v>
       </c>
     </row>
     <row r="38">
@@ -2463,24 +2353,24 @@
         </is>
       </c>
       <c r="G38">
-        <v>0.4761904761904755</v>
-      </c>
-      <c r="H38" t="inlineStr">
+        <v>2047</v>
+      </c>
+      <c r="H38">
+        <v>0.625</v>
+      </c>
+      <c r="I38" t="inlineStr">
         <is>
           <t>60-80</t>
         </is>
       </c>
-      <c r="I38">
-        <v>2015</v>
-      </c>
       <c r="J38">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="K38">
         <v>0.8</v>
       </c>
       <c r="L38">
-        <v>0.3366666666666697</v>
+        <v>0.9</v>
       </c>
       <c r="M38" t="inlineStr">
         <is>
@@ -2493,15 +2383,10 @@
         </is>
       </c>
       <c r="O38">
-        <v>0.9</v>
+        <v>2015</v>
       </c>
       <c r="P38">
-        <v>2050</v>
-      </c>
-      <c r="Q38" t="inlineStr">
-        <is>
-          <t>future</t>
-        </is>
+        <v>0.7400000000000001</v>
       </c>
     </row>
     <row r="39">
@@ -2529,16 +2414,13 @@
           <t>DEU</t>
         </is>
       </c>
-      <c r="G39">
-        <v>0</v>
-      </c>
-      <c r="H39" t="inlineStr">
+      <c r="H39">
+        <v>0</v>
+      </c>
+      <c r="I39" t="inlineStr">
         <is>
           <t>80-100</t>
         </is>
-      </c>
-      <c r="I39">
-        <v>2015</v>
       </c>
       <c r="J39">
         <v>2020</v>
@@ -2547,7 +2429,7 @@
         <v>0.6000000000000001</v>
       </c>
       <c r="L39">
-        <v>0.55</v>
+        <v>0.6000000000000001</v>
       </c>
       <c r="M39" t="inlineStr">
         <is>
@@ -2560,12 +2442,10 @@
         </is>
       </c>
       <c r="O39">
-        <v>0.6000000000000001</v>
-      </c>
-      <c r="Q39" t="inlineStr">
-        <is>
-          <t>never</t>
-        </is>
+        <v>2015</v>
+      </c>
+      <c r="P39">
+        <v>0.5</v>
       </c>
     </row>
     <row r="40">
@@ -2635,43 +2515,38 @@
           <t>DNK</t>
         </is>
       </c>
-      <c r="G41">
-        <v>0</v>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>60-80</t>
-        </is>
-      </c>
-      <c r="I41">
+      <c r="H41">
+        <v>-0.625</v>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>0-20</t>
+        </is>
+      </c>
+      <c r="J41">
+        <v>2023</v>
+      </c>
+      <c r="K41">
+        <v>0.8</v>
+      </c>
+      <c r="L41">
+        <v>0.7000000000000001</v>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>10.1.1</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>Prosperity gap (average shortfall from a prosperity standard of $25/day)</t>
+        </is>
+      </c>
+      <c r="O41">
         <v>2015</v>
       </c>
-      <c r="J41">
-        <v>2022</v>
-      </c>
-      <c r="K41">
-        <v>0.7000000000000001</v>
-      </c>
-      <c r="L41">
-        <v>0.27</v>
-      </c>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>10.1.1</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr">
-        <is>
-          <t>Prosperity gap (average shortfall from a prosperity standard of $25/day)</t>
-        </is>
-      </c>
-      <c r="O41">
-        <v>0.7000000000000001</v>
-      </c>
-      <c r="Q41" t="inlineStr">
-        <is>
-          <t>never</t>
-        </is>
+      <c r="P41">
+        <v>0.54</v>
       </c>
     </row>
     <row r="42">
@@ -2700,45 +2575,40 @@
         </is>
       </c>
       <c r="G42">
-        <v>0.9598214285714288</v>
-      </c>
-      <c r="H42" t="inlineStr">
+        <v>2057</v>
+      </c>
+      <c r="H42">
+        <v>1.560846560846561</v>
+      </c>
+      <c r="I42" t="inlineStr">
         <is>
           <t>40-60</t>
         </is>
       </c>
-      <c r="I42">
+      <c r="J42">
+        <v>2024</v>
+      </c>
+      <c r="K42">
+        <v>2.1</v>
+      </c>
+      <c r="L42">
+        <v>3</v>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>10.1.1</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>Prosperity gap (average shortfall from a prosperity standard of $25/day)</t>
+        </is>
+      </c>
+      <c r="O42">
         <v>2015</v>
       </c>
-      <c r="J42">
-        <v>2023</v>
-      </c>
-      <c r="K42">
-        <v>2.4</v>
-      </c>
-      <c r="L42">
-        <v>1.019523809523816</v>
-      </c>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>10.1.1</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr">
-        <is>
-          <t>Prosperity gap (average shortfall from a prosperity standard of $25/day)</t>
-        </is>
-      </c>
-      <c r="O42">
-        <v>3</v>
-      </c>
       <c r="P42">
-        <v>2069</v>
-      </c>
-      <c r="Q42" t="inlineStr">
-        <is>
-          <t>future</t>
-        </is>
+        <v>2.402857142857143</v>
       </c>
     </row>
     <row r="43">
@@ -2808,46 +2678,38 @@
           <t>ECU</t>
         </is>
       </c>
-      <c r="G44">
-        <v>0.15625</v>
-      </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>20-40</t>
-        </is>
-      </c>
-      <c r="I44">
+      <c r="H44">
+        <v>-0.1234567901234571</v>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>0-20</t>
+        </is>
+      </c>
+      <c r="J44">
+        <v>2024</v>
+      </c>
+      <c r="K44">
+        <v>3.5</v>
+      </c>
+      <c r="L44">
+        <v>3.4</v>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>10.1.1</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>Prosperity gap (average shortfall from a prosperity standard of $25/day)</t>
+        </is>
+      </c>
+      <c r="O44">
         <v>2015</v>
       </c>
-      <c r="J44">
-        <v>2023</v>
-      </c>
-      <c r="K44">
-        <v>3.3</v>
-      </c>
-      <c r="L44">
-        <v>1.224404761904771</v>
-      </c>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>10.1.1</t>
-        </is>
-      </c>
-      <c r="N44" t="inlineStr">
-        <is>
-          <t>Prosperity gap (average shortfall from a prosperity standard of $25/day)</t>
-        </is>
-      </c>
-      <c r="O44">
-        <v>3.4</v>
-      </c>
       <c r="P44">
-        <v>2378</v>
-      </c>
-      <c r="Q44" t="inlineStr">
-        <is>
-          <t>future</t>
-        </is>
+        <v>2.719999999999997</v>
       </c>
     </row>
     <row r="45">
@@ -2875,16 +2737,13 @@
           <t>EGY</t>
         </is>
       </c>
-      <c r="G45">
-        <v>0</v>
-      </c>
-      <c r="H45" t="inlineStr">
+      <c r="H45">
+        <v>0</v>
+      </c>
+      <c r="I45" t="inlineStr">
         <is>
           <t>20-40</t>
         </is>
-      </c>
-      <c r="I45">
-        <v>2015</v>
       </c>
       <c r="J45">
         <v>2021</v>
@@ -2893,7 +2752,7 @@
         <v>3.9</v>
       </c>
       <c r="L45">
-        <v>2.044999999999978</v>
+        <v>3.9</v>
       </c>
       <c r="M45" t="inlineStr">
         <is>
@@ -2906,12 +2765,10 @@
         </is>
       </c>
       <c r="O45">
-        <v>3.9</v>
-      </c>
-      <c r="Q45" t="inlineStr">
-        <is>
-          <t>never</t>
-        </is>
+        <v>2015</v>
+      </c>
+      <c r="P45">
+        <v>3.355555555555548</v>
       </c>
     </row>
     <row r="46">
@@ -2940,24 +2797,24 @@
         </is>
       </c>
       <c r="G46">
-        <v>0.5714285714285714</v>
-      </c>
-      <c r="H46" t="inlineStr">
+        <v>2076</v>
+      </c>
+      <c r="H46">
+        <v>0.625</v>
+      </c>
+      <c r="I46" t="inlineStr">
         <is>
           <t>60-80</t>
         </is>
       </c>
-      <c r="I46">
-        <v>2015</v>
-      </c>
       <c r="J46">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="K46">
         <v>1.3</v>
       </c>
       <c r="L46">
-        <v>0.5433333333333394</v>
+        <v>1.5</v>
       </c>
       <c r="M46" t="inlineStr">
         <is>
@@ -2970,15 +2827,10 @@
         </is>
       </c>
       <c r="O46">
-        <v>1.5</v>
+        <v>2015</v>
       </c>
       <c r="P46">
-        <v>2068</v>
-      </c>
-      <c r="Q46" t="inlineStr">
-        <is>
-          <t>future</t>
-        </is>
+        <v>1.209999999999998</v>
       </c>
     </row>
     <row r="47">
@@ -3007,45 +2859,40 @@
         </is>
       </c>
       <c r="G47">
-        <v>0.8571428571428571</v>
-      </c>
-      <c r="H47" t="inlineStr">
+        <v>2035</v>
+      </c>
+      <c r="H47">
+        <v>1.875</v>
+      </c>
+      <c r="I47" t="inlineStr">
         <is>
           <t>60-80</t>
         </is>
       </c>
-      <c r="I47">
+      <c r="J47">
+        <v>2023</v>
+      </c>
+      <c r="K47">
+        <v>1</v>
+      </c>
+      <c r="L47">
+        <v>1.5</v>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>10.1.1</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>Prosperity gap (average shortfall from a prosperity standard of $25/day)</t>
+        </is>
+      </c>
+      <c r="O47">
         <v>2015</v>
       </c>
-      <c r="J47">
-        <v>2022</v>
-      </c>
-      <c r="K47">
-        <v>1.2</v>
-      </c>
-      <c r="L47">
-        <v>0.5433333333333394</v>
-      </c>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>10.1.1</t>
-        </is>
-      </c>
-      <c r="N47" t="inlineStr">
-        <is>
-          <t>Prosperity gap (average shortfall from a prosperity standard of $25/day)</t>
-        </is>
-      </c>
-      <c r="O47">
-        <v>1.5</v>
-      </c>
       <c r="P47">
-        <v>2050</v>
-      </c>
-      <c r="Q47" t="inlineStr">
-        <is>
-          <t>future</t>
-        </is>
+        <v>1.209999999999998</v>
       </c>
     </row>
     <row r="48">
@@ -3073,16 +2920,13 @@
           <t>ETH</t>
         </is>
       </c>
-      <c r="G48">
-        <v>-0.2726774433296173</v>
-      </c>
-      <c r="H48" t="inlineStr">
+      <c r="H48">
+        <v>-0.2964426877470352</v>
+      </c>
+      <c r="I48" t="inlineStr">
         <is>
           <t>20-40</t>
         </is>
-      </c>
-      <c r="I48">
-        <v>2015</v>
       </c>
       <c r="J48">
         <v>2021</v>
@@ -3091,7 +2935,7 @@
         <v>9.1</v>
       </c>
       <c r="L48">
-        <v>5.989770998265586</v>
+        <v>8.700000000000001</v>
       </c>
       <c r="M48" t="inlineStr">
         <is>
@@ -3104,12 +2948,10 @@
         </is>
       </c>
       <c r="O48">
-        <v>8.700000000000001</v>
-      </c>
-      <c r="Q48" t="inlineStr">
-        <is>
-          <t>never</t>
-        </is>
+        <v>2015</v>
+      </c>
+      <c r="P48">
+        <v>7.484155844155842</v>
       </c>
     </row>
     <row r="49">
@@ -3137,43 +2979,38 @@
           <t>FIN</t>
         </is>
       </c>
-      <c r="G49">
-        <v>0</v>
-      </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>80-100</t>
-        </is>
-      </c>
-      <c r="I49">
+      <c r="H49">
+        <v>-0.625</v>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>0-20</t>
+        </is>
+      </c>
+      <c r="J49">
+        <v>2023</v>
+      </c>
+      <c r="K49">
+        <v>0.7000000000000001</v>
+      </c>
+      <c r="L49">
+        <v>0.6000000000000001</v>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>10.1.1</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>Prosperity gap (average shortfall from a prosperity standard of $25/day)</t>
+        </is>
+      </c>
+      <c r="O49">
         <v>2015</v>
       </c>
-      <c r="J49">
-        <v>2022</v>
-      </c>
-      <c r="K49">
-        <v>0.6000000000000001</v>
-      </c>
-      <c r="L49">
-        <v>0.22</v>
-      </c>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>10.1.1</t>
-        </is>
-      </c>
-      <c r="N49" t="inlineStr">
-        <is>
-          <t>Prosperity gap (average shortfall from a prosperity standard of $25/day)</t>
-        </is>
-      </c>
-      <c r="O49">
-        <v>0.6000000000000001</v>
-      </c>
-      <c r="Q49" t="inlineStr">
-        <is>
-          <t>never</t>
-        </is>
+      <c r="P49">
+        <v>0.44</v>
       </c>
     </row>
     <row r="50">
@@ -3243,25 +3080,22 @@
           <t>FRA</t>
         </is>
       </c>
-      <c r="G51">
-        <v>0</v>
-      </c>
-      <c r="H51" t="inlineStr">
+      <c r="H51">
+        <v>0</v>
+      </c>
+      <c r="I51" t="inlineStr">
         <is>
           <t>80-100</t>
         </is>
       </c>
-      <c r="I51">
-        <v>2015</v>
-      </c>
       <c r="J51">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="K51">
         <v>0.6000000000000001</v>
       </c>
       <c r="L51">
-        <v>0.22</v>
+        <v>0.6000000000000001</v>
       </c>
       <c r="M51" t="inlineStr">
         <is>
@@ -3274,12 +3108,10 @@
         </is>
       </c>
       <c r="O51">
-        <v>0.6000000000000001</v>
-      </c>
-      <c r="Q51" t="inlineStr">
-        <is>
-          <t>never</t>
-        </is>
+        <v>2015</v>
+      </c>
+      <c r="P51">
+        <v>0.44</v>
       </c>
     </row>
     <row r="52">
@@ -3391,16 +3223,13 @@
           <t>GBR</t>
         </is>
       </c>
-      <c r="G54">
-        <v>-0.5555555555555548</v>
-      </c>
-      <c r="H54" t="inlineStr">
+      <c r="H54">
+        <v>-0.8333333333333334</v>
+      </c>
+      <c r="I54" t="inlineStr">
         <is>
           <t>0-20</t>
         </is>
-      </c>
-      <c r="I54">
-        <v>2015</v>
       </c>
       <c r="J54">
         <v>2021</v>
@@ -3409,7 +3238,7 @@
         <v>0.9</v>
       </c>
       <c r="L54">
-        <v>0.3433333333333303</v>
+        <v>0.8</v>
       </c>
       <c r="M54" t="inlineStr">
         <is>
@@ -3422,12 +3251,10 @@
         </is>
       </c>
       <c r="O54">
-        <v>0.8</v>
-      </c>
-      <c r="Q54" t="inlineStr">
-        <is>
-          <t>never</t>
-        </is>
+        <v>2015</v>
+      </c>
+      <c r="P54">
+        <v>0.68</v>
       </c>
     </row>
     <row r="55">
@@ -3456,45 +3283,40 @@
         </is>
       </c>
       <c r="G55">
-        <v>1.919642857142857</v>
-      </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>40-60</t>
-        </is>
-      </c>
-      <c r="I55">
+        <v>2078</v>
+      </c>
+      <c r="H55">
+        <v>1.389795389795391</v>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>60-80</t>
+        </is>
+      </c>
+      <c r="J55">
+        <v>2024</v>
+      </c>
+      <c r="K55">
+        <v>3.8</v>
+      </c>
+      <c r="L55">
+        <v>5.2</v>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>10.1.1</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>Prosperity gap (average shortfall from a prosperity standard of $25/day)</t>
+        </is>
+      </c>
+      <c r="O55">
         <v>2015</v>
       </c>
-      <c r="J55">
-        <v>2023</v>
-      </c>
-      <c r="K55">
-        <v>4.100000000000001</v>
-      </c>
-      <c r="L55">
-        <v>2.76857142857145</v>
-      </c>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>10.1.1</t>
-        </is>
-      </c>
-      <c r="N55" t="inlineStr">
-        <is>
-          <t>Prosperity gap (average shortfall from a prosperity standard of $25/day)</t>
-        </is>
-      </c>
-      <c r="O55">
-        <v>5.2</v>
-      </c>
       <c r="P55">
-        <v>2057</v>
-      </c>
-      <c r="Q55" t="inlineStr">
-        <is>
-          <t>future</t>
-        </is>
+        <v>4.150815850815843</v>
       </c>
     </row>
     <row r="56">
@@ -3606,16 +3428,13 @@
           <t>GMB</t>
         </is>
       </c>
-      <c r="G58">
-        <v>-1.166666666666667</v>
-      </c>
-      <c r="H58" t="inlineStr">
+      <c r="H58">
+        <v>-0.6029411764705884</v>
+      </c>
+      <c r="I58" t="inlineStr">
         <is>
           <t>0-20</t>
         </is>
-      </c>
-      <c r="I58">
-        <v>2015</v>
       </c>
       <c r="J58">
         <v>2020</v>
@@ -3624,7 +3443,7 @@
         <v>6.9</v>
       </c>
       <c r="L58">
-        <v>4.974999999999985</v>
+        <v>6.4</v>
       </c>
       <c r="M58" t="inlineStr">
         <is>
@@ -3637,12 +3456,10 @@
         </is>
       </c>
       <c r="O58">
-        <v>6.4</v>
-      </c>
-      <c r="Q58" t="inlineStr">
-        <is>
-          <t>never</t>
-        </is>
+        <v>2015</v>
+      </c>
+      <c r="P58">
+        <v>5.648333333333326</v>
       </c>
     </row>
     <row r="59">
@@ -3755,45 +3572,40 @@
         </is>
       </c>
       <c r="G61">
-        <v>1.850340136054421</v>
-      </c>
-      <c r="H61" t="inlineStr">
+        <v>2037</v>
+      </c>
+      <c r="H61">
+        <v>2.458333333333334</v>
+      </c>
+      <c r="I61" t="inlineStr">
         <is>
           <t>80-100</t>
         </is>
       </c>
-      <c r="I61">
+      <c r="J61">
+        <v>2023</v>
+      </c>
+      <c r="K61">
+        <v>1.3</v>
+      </c>
+      <c r="L61">
+        <v>2.2</v>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>10.1.1</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>Prosperity gap (average shortfall from a prosperity standard of $25/day)</t>
+        </is>
+      </c>
+      <c r="O61">
         <v>2015</v>
       </c>
-      <c r="J61">
-        <v>2022</v>
-      </c>
-      <c r="K61">
-        <v>1.4</v>
-      </c>
-      <c r="L61">
-        <v>0.7935714285714397</v>
-      </c>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>10.1.1</t>
-        </is>
-      </c>
-      <c r="N61" t="inlineStr">
-        <is>
-          <t>Prosperity gap (average shortfall from a prosperity standard of $25/day)</t>
-        </is>
-      </c>
-      <c r="O61">
-        <v>2.2</v>
-      </c>
       <c r="P61">
-        <v>2037</v>
-      </c>
-      <c r="Q61" t="inlineStr">
-        <is>
-          <t>future</t>
-        </is>
+        <v>1.783333333333337</v>
       </c>
     </row>
     <row r="62">
@@ -3948,42 +3760,40 @@
         </is>
       </c>
       <c r="G65">
-        <v>-0.15625</v>
-      </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>0-20</t>
-        </is>
-      </c>
-      <c r="I65">
+        <v>2477</v>
+      </c>
+      <c r="H65">
+        <v>0.2083333333333333</v>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>20-40</t>
+        </is>
+      </c>
+      <c r="J65">
+        <v>2024</v>
+      </c>
+      <c r="K65">
+        <v>6.2</v>
+      </c>
+      <c r="L65">
+        <v>6.5</v>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>10.1.1</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>Prosperity gap (average shortfall from a prosperity standard of $25/day)</t>
+        </is>
+      </c>
+      <c r="O65">
         <v>2015</v>
       </c>
-      <c r="J65">
-        <v>2023</v>
-      </c>
-      <c r="K65">
-        <v>6.600000000000001</v>
-      </c>
-      <c r="L65">
-        <v>4.21142857142855</v>
-      </c>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>10.1.1</t>
-        </is>
-      </c>
-      <c r="N65" t="inlineStr">
-        <is>
-          <t>Prosperity gap (average shortfall from a prosperity standard of $25/day)</t>
-        </is>
-      </c>
-      <c r="O65">
-        <v>6.5</v>
-      </c>
-      <c r="Q65" t="inlineStr">
-        <is>
-          <t>never</t>
-        </is>
+      <c r="P65">
+        <v>5.191845238095238</v>
       </c>
     </row>
     <row r="66">
@@ -4012,45 +3822,40 @@
         </is>
       </c>
       <c r="G66">
-        <v>1.523809523809524</v>
-      </c>
-      <c r="H66" t="inlineStr">
+        <v>2033</v>
+      </c>
+      <c r="H66">
+        <v>2.583333333333332</v>
+      </c>
+      <c r="I66" t="inlineStr">
         <is>
           <t>60-80</t>
         </is>
       </c>
-      <c r="I66">
+      <c r="J66">
+        <v>2023</v>
+      </c>
+      <c r="K66">
+        <v>1.1</v>
+      </c>
+      <c r="L66">
+        <v>1.9</v>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>10.1.1</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>Prosperity gap (average shortfall from a prosperity standard of $25/day)</t>
+        </is>
+      </c>
+      <c r="O66">
         <v>2015</v>
       </c>
-      <c r="J66">
-        <v>2022</v>
-      </c>
-      <c r="K66">
-        <v>1.3</v>
-      </c>
-      <c r="L66">
-        <v>0.6766666666666606</v>
-      </c>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>10.1.1</t>
-        </is>
-      </c>
-      <c r="N66" t="inlineStr">
-        <is>
-          <t>Prosperity gap (average shortfall from a prosperity standard of $25/day)</t>
-        </is>
-      </c>
-      <c r="O66">
-        <v>1.9</v>
-      </c>
       <c r="P66">
-        <v>2039</v>
-      </c>
-      <c r="Q66" t="inlineStr">
-        <is>
-          <t>future</t>
-        </is>
+        <v>1.54</v>
       </c>
     </row>
     <row r="67">
@@ -4120,25 +3925,11 @@
           <t>HUN</t>
         </is>
       </c>
-      <c r="G68">
-        <v>1.4421768707483</v>
-      </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>60-80</t>
-        </is>
-      </c>
-      <c r="I68">
-        <v>2015</v>
-      </c>
       <c r="J68">
-        <v>2022</v>
+        <v>2017</v>
       </c>
       <c r="K68">
-        <v>1.4</v>
-      </c>
-      <c r="L68">
-        <v>0.7078571428571384</v>
+        <v>1.9</v>
       </c>
       <c r="M68" t="inlineStr">
         <is>
@@ -4148,17 +3939,6 @@
       <c r="N68" t="inlineStr">
         <is>
           <t>Prosperity gap (average shortfall from a prosperity standard of $25/day)</t>
-        </is>
-      </c>
-      <c r="O68">
-        <v>2</v>
-      </c>
-      <c r="P68">
-        <v>2042</v>
-      </c>
-      <c r="Q68" t="inlineStr">
-        <is>
-          <t>future</t>
         </is>
       </c>
     </row>
@@ -4188,45 +3968,40 @@
         </is>
       </c>
       <c r="G69">
-        <v>3.04563492063492</v>
-      </c>
-      <c r="H69" t="inlineStr">
+        <v>2078</v>
+      </c>
+      <c r="H69">
+        <v>1.549318872848285</v>
+      </c>
+      <c r="I69" t="inlineStr">
         <is>
           <t>60-80</t>
         </is>
       </c>
-      <c r="I69">
+      <c r="J69">
+        <v>2024</v>
+      </c>
+      <c r="K69">
+        <v>4.800000000000001</v>
+      </c>
+      <c r="L69">
+        <v>6.800000000000001</v>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>10.1.1</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>Prosperity gap (average shortfall from a prosperity standard of $25/day)</t>
+        </is>
+      </c>
+      <c r="O69">
         <v>2015</v>
       </c>
-      <c r="J69">
-        <v>2023</v>
-      </c>
-      <c r="K69">
-        <v>5</v>
-      </c>
-      <c r="L69">
-        <v>4.465555555555551</v>
-      </c>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>10.1.1</t>
-        </is>
-      </c>
-      <c r="N69" t="inlineStr">
-        <is>
-          <t>Prosperity gap (average shortfall from a prosperity standard of $25/day)</t>
-        </is>
-      </c>
-      <c r="O69">
-        <v>6.800000000000001</v>
-      </c>
       <c r="P69">
-        <v>2049</v>
-      </c>
-      <c r="Q69" t="inlineStr">
-        <is>
-          <t>future</t>
-        </is>
+        <v>5.428039215686274</v>
       </c>
     </row>
     <row r="70">
@@ -4297,24 +4072,24 @@
         </is>
       </c>
       <c r="G71">
-        <v>1.666666666666667</v>
-      </c>
-      <c r="H71" t="inlineStr">
+        <v>2028</v>
+      </c>
+      <c r="H71">
+        <v>2.083333333333334</v>
+      </c>
+      <c r="I71" t="inlineStr">
         <is>
           <t>60-80</t>
         </is>
       </c>
-      <c r="I71">
-        <v>2015</v>
-      </c>
       <c r="J71">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="K71">
         <v>0.7000000000000001</v>
       </c>
       <c r="L71">
-        <v>0.3866666666666697</v>
+        <v>1.1</v>
       </c>
       <c r="M71" t="inlineStr">
         <is>
@@ -4327,15 +4102,10 @@
         </is>
       </c>
       <c r="O71">
-        <v>1.1</v>
+        <v>2015</v>
       </c>
       <c r="P71">
-        <v>2028</v>
-      </c>
-      <c r="Q71" t="inlineStr">
-        <is>
-          <t>future</t>
-        </is>
+        <v>0.8733333333333348</v>
       </c>
     </row>
     <row r="72">
@@ -4364,15 +4134,15 @@
         </is>
       </c>
       <c r="G72">
-        <v>0.3125</v>
-      </c>
-      <c r="H72" t="inlineStr">
+        <v>2257</v>
+      </c>
+      <c r="H72">
+        <v>0.2951388888888893</v>
+      </c>
+      <c r="I72" t="inlineStr">
         <is>
           <t>20-40</t>
         </is>
-      </c>
-      <c r="I72">
-        <v>2015</v>
       </c>
       <c r="J72">
         <v>2023</v>
@@ -4381,7 +4151,7 @@
         <v>3.3</v>
       </c>
       <c r="L72">
-        <v>1.286904761904771</v>
+        <v>3.5</v>
       </c>
       <c r="M72" t="inlineStr">
         <is>
@@ -4394,15 +4164,10 @@
         </is>
       </c>
       <c r="O72">
-        <v>3.5</v>
+        <v>2015</v>
       </c>
       <c r="P72">
-        <v>2200</v>
-      </c>
-      <c r="Q72" t="inlineStr">
-        <is>
-          <t>future</t>
-        </is>
+        <v>2.867777777777783</v>
       </c>
     </row>
     <row r="73">
@@ -4473,10 +4238,10 @@
         </is>
       </c>
       <c r="J74">
-        <v>2018</v>
+        <v>2019</v>
       </c>
       <c r="K74">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="M74" t="inlineStr">
         <is>
@@ -4515,15 +4280,15 @@
         </is>
       </c>
       <c r="G75">
-        <v>0.6666666666666666</v>
-      </c>
-      <c r="H75" t="inlineStr">
+        <v>2052</v>
+      </c>
+      <c r="H75">
+        <v>0.9722222222222214</v>
+      </c>
+      <c r="I75" t="inlineStr">
         <is>
           <t>60-80</t>
         </is>
-      </c>
-      <c r="I75">
-        <v>2015</v>
       </c>
       <c r="J75">
         <v>2021</v>
@@ -4532,7 +4297,7 @@
         <v>1.2</v>
       </c>
       <c r="L75">
-        <v>0.5833333333333395</v>
+        <v>1.4</v>
       </c>
       <c r="M75" t="inlineStr">
         <is>
@@ -4545,15 +4310,10 @@
         </is>
       </c>
       <c r="O75">
-        <v>1.4</v>
+        <v>2015</v>
       </c>
       <c r="P75">
-        <v>2057</v>
-      </c>
-      <c r="Q75" t="inlineStr">
-        <is>
-          <t>future</t>
-        </is>
+        <v>1.194999999999998</v>
       </c>
     </row>
     <row r="76">
@@ -4582,45 +4342,40 @@
         </is>
       </c>
       <c r="G76">
-        <v>2.217687074829933</v>
-      </c>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>80-100</t>
-        </is>
-      </c>
-      <c r="I76">
+        <v>2041</v>
+      </c>
+      <c r="H76">
+        <v>1.9375</v>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>60-80</t>
+        </is>
+      </c>
+      <c r="J76">
+        <v>2023</v>
+      </c>
+      <c r="K76">
+        <v>1.4</v>
+      </c>
+      <c r="L76">
+        <v>2.1</v>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>10.1.1</t>
+        </is>
+      </c>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>Prosperity gap (average shortfall from a prosperity standard of $25/day)</t>
+        </is>
+      </c>
+      <c r="O76">
         <v>2015</v>
       </c>
-      <c r="J76">
-        <v>2022</v>
-      </c>
-      <c r="K76">
-        <v>1.2</v>
-      </c>
-      <c r="L76">
-        <v>0.7507142857142891</v>
-      </c>
-      <c r="M76" t="inlineStr">
-        <is>
-          <t>10.1.1</t>
-        </is>
-      </c>
-      <c r="N76" t="inlineStr">
-        <is>
-          <t>Prosperity gap (average shortfall from a prosperity standard of $25/day)</t>
-        </is>
-      </c>
-      <c r="O76">
-        <v>2.1</v>
-      </c>
       <c r="P76">
-        <v>2033</v>
-      </c>
-      <c r="Q76" t="inlineStr">
-        <is>
-          <t>future</t>
-        </is>
+        <v>1.7</v>
       </c>
     </row>
     <row r="77">
@@ -4732,16 +4487,13 @@
           <t>JPN</t>
         </is>
       </c>
-      <c r="G79">
-        <v>-1.5</v>
-      </c>
-      <c r="H79" t="inlineStr">
+      <c r="H79">
+        <v>-2</v>
+      </c>
+      <c r="I79" t="inlineStr">
         <is>
           <t>0-20</t>
         </is>
-      </c>
-      <c r="I79">
-        <v>2015</v>
       </c>
       <c r="J79">
         <v>2020</v>
@@ -4750,7 +4502,7 @@
         <v>1.2</v>
       </c>
       <c r="L79">
-        <v>0.4333333333333394</v>
+        <v>0.9</v>
       </c>
       <c r="M79" t="inlineStr">
         <is>
@@ -4763,12 +4515,10 @@
         </is>
       </c>
       <c r="O79">
-        <v>0.9</v>
-      </c>
-      <c r="Q79" t="inlineStr">
-        <is>
-          <t>never</t>
-        </is>
+        <v>2015</v>
+      </c>
+      <c r="P79">
+        <v>0.8</v>
       </c>
     </row>
     <row r="80">
@@ -4797,15 +4547,15 @@
         </is>
       </c>
       <c r="G80">
-        <v>0.4464285714285718</v>
-      </c>
-      <c r="H80" t="inlineStr">
+        <v>2122</v>
+      </c>
+      <c r="H80">
+        <v>0.5555555555555571</v>
+      </c>
+      <c r="I80" t="inlineStr">
         <is>
           <t>40-60</t>
         </is>
-      </c>
-      <c r="I80">
-        <v>2015</v>
       </c>
       <c r="J80">
         <v>2021</v>
@@ -4814,7 +4564,7 @@
         <v>2.4</v>
       </c>
       <c r="L80">
-        <v>1.139523809523816</v>
+        <v>2.6</v>
       </c>
       <c r="M80" t="inlineStr">
         <is>
@@ -4827,15 +4577,10 @@
         </is>
       </c>
       <c r="O80">
-        <v>2.6</v>
+        <v>2015</v>
       </c>
       <c r="P80">
-        <v>2120</v>
-      </c>
-      <c r="Q80" t="inlineStr">
-        <is>
-          <t>future</t>
-        </is>
+        <v>2.240000000000003</v>
       </c>
     </row>
     <row r="81">
@@ -4863,25 +4608,22 @@
           <t>KEN</t>
         </is>
       </c>
-      <c r="G81">
-        <v>-0.4131148902851939</v>
-      </c>
-      <c r="H81" t="inlineStr">
+      <c r="H81">
+        <v>-0.4716356107660452</v>
+      </c>
+      <c r="I81" t="inlineStr">
         <is>
           <t>0-20</t>
         </is>
       </c>
-      <c r="I81">
-        <v>2015</v>
-      </c>
       <c r="J81">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="K81">
         <v>10</v>
       </c>
       <c r="L81">
-        <v>6.130221450389952</v>
+        <v>9.200000000000001</v>
       </c>
       <c r="M81" t="inlineStr">
         <is>
@@ -4894,12 +4636,10 @@
         </is>
       </c>
       <c r="O81">
-        <v>9.200000000000001</v>
-      </c>
-      <c r="Q81" t="inlineStr">
-        <is>
-          <t>never</t>
-        </is>
+        <v>2015</v>
+      </c>
+      <c r="P81">
+        <v>7.714709203839634</v>
       </c>
     </row>
     <row r="82">
@@ -4928,45 +4668,40 @@
         </is>
       </c>
       <c r="G82">
-        <v>2.040816326530612</v>
-      </c>
-      <c r="H82" t="inlineStr">
+        <v>2087</v>
+      </c>
+      <c r="H82">
+        <v>1.304258241758243</v>
+      </c>
+      <c r="I82" t="inlineStr">
         <is>
           <t>40-60</t>
         </is>
       </c>
-      <c r="I82">
+      <c r="J82">
+        <v>2023</v>
+      </c>
+      <c r="K82">
+        <v>4.7</v>
+      </c>
+      <c r="L82">
+        <v>6.100000000000001</v>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>10.1.1</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>Prosperity gap (average shortfall from a prosperity standard of $25/day)</t>
+        </is>
+      </c>
+      <c r="O82">
         <v>2015</v>
       </c>
-      <c r="J82">
-        <v>2022</v>
-      </c>
-      <c r="K82">
-        <v>5.100000000000001</v>
-      </c>
-      <c r="L82">
-        <v>4.117142857142826</v>
-      </c>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>10.1.1</t>
-        </is>
-      </c>
-      <c r="N82" t="inlineStr">
-        <is>
-          <t>Prosperity gap (average shortfall from a prosperity standard of $25/day)</t>
-        </is>
-      </c>
-      <c r="O82">
-        <v>6.100000000000001</v>
-      </c>
       <c r="P82">
-        <v>2061</v>
-      </c>
-      <c r="Q82" t="inlineStr">
-        <is>
-          <t>future</t>
-        </is>
+        <v>4.992087912087918</v>
       </c>
     </row>
     <row r="83">
@@ -5037,10 +4772,10 @@
         </is>
       </c>
       <c r="G84">
-        <v>1.666666666666669</v>
-      </c>
-      <c r="I84">
-        <v>2016</v>
+        <v>2024</v>
+      </c>
+      <c r="H84">
+        <v>2</v>
       </c>
       <c r="J84">
         <v>2021</v>
@@ -5049,7 +4784,7 @@
         <v>0.6000000000000001</v>
       </c>
       <c r="L84">
-        <v>0.3833333333333303</v>
+        <v>0.8</v>
       </c>
       <c r="M84" t="inlineStr">
         <is>
@@ -5062,15 +4797,10 @@
         </is>
       </c>
       <c r="O84">
-        <v>0.8</v>
+        <v>2016</v>
       </c>
       <c r="P84">
-        <v>2024</v>
-      </c>
-      <c r="Q84" t="inlineStr">
-        <is>
-          <t>future</t>
-        </is>
+        <v>0.7000000000000001</v>
       </c>
     </row>
     <row r="85">
@@ -5141,10 +4871,10 @@
         </is>
       </c>
       <c r="J86">
-        <v>2011</v>
+        <v>2022</v>
       </c>
       <c r="K86">
-        <v>1.6</v>
+        <v>4.2</v>
       </c>
       <c r="M86" t="inlineStr">
         <is>
@@ -5351,45 +5081,40 @@
         </is>
       </c>
       <c r="G91">
-        <v>1.80952380952381</v>
-      </c>
-      <c r="H91" t="inlineStr">
-        <is>
-          <t>80-100</t>
-        </is>
-      </c>
-      <c r="I91">
+        <v>2073</v>
+      </c>
+      <c r="H91">
+        <v>0.8125</v>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>40-60</t>
+        </is>
+      </c>
+      <c r="J91">
+        <v>2023</v>
+      </c>
+      <c r="K91">
+        <v>1.6</v>
+      </c>
+      <c r="L91">
+        <v>1.9</v>
+      </c>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>10.1.1</t>
+        </is>
+      </c>
+      <c r="N91" t="inlineStr">
+        <is>
+          <t>Prosperity gap (average shortfall from a prosperity standard of $25/day)</t>
+        </is>
+      </c>
+      <c r="O91">
         <v>2015</v>
       </c>
-      <c r="J91">
-        <v>2022</v>
-      </c>
-      <c r="K91">
-        <v>1.2</v>
-      </c>
-      <c r="L91">
-        <v>0.6766666666666606</v>
-      </c>
-      <c r="M91" t="inlineStr">
-        <is>
-          <t>10.1.1</t>
-        </is>
-      </c>
-      <c r="N91" t="inlineStr">
-        <is>
-          <t>Prosperity gap (average shortfall from a prosperity standard of $25/day)</t>
-        </is>
-      </c>
-      <c r="O91">
-        <v>1.9</v>
-      </c>
       <c r="P91">
-        <v>2035</v>
-      </c>
-      <c r="Q91" t="inlineStr">
-        <is>
-          <t>future</t>
-        </is>
+        <v>1.54</v>
       </c>
     </row>
     <row r="92">
@@ -5418,24 +5143,24 @@
         </is>
       </c>
       <c r="G92">
-        <v>2.142857142857143</v>
-      </c>
-      <c r="H92" t="inlineStr">
+        <v>2019</v>
+      </c>
+      <c r="H92">
+        <v>1.875</v>
+      </c>
+      <c r="I92" t="inlineStr">
         <is>
           <t>80-100</t>
         </is>
       </c>
-      <c r="I92">
-        <v>2015</v>
-      </c>
       <c r="J92">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="K92">
         <v>0.4</v>
       </c>
       <c r="L92">
-        <v>0.27</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="M92" t="inlineStr">
         <is>
@@ -5448,15 +5173,10 @@
         </is>
       </c>
       <c r="O92">
-        <v>0.7000000000000001</v>
+        <v>2015</v>
       </c>
       <c r="P92">
-        <v>2019</v>
-      </c>
-      <c r="Q92" t="inlineStr">
-        <is>
-          <t>past</t>
-        </is>
+        <v>0.54</v>
       </c>
     </row>
     <row r="93">
@@ -5485,45 +5205,40 @@
         </is>
       </c>
       <c r="G93">
-        <v>1.571428571428571</v>
-      </c>
-      <c r="H93" t="inlineStr">
+        <v>2045</v>
+      </c>
+      <c r="H93">
+        <v>1.5</v>
+      </c>
+      <c r="I93" t="inlineStr">
         <is>
           <t>60-80</t>
         </is>
       </c>
-      <c r="I93">
+      <c r="J93">
+        <v>2023</v>
+      </c>
+      <c r="K93">
+        <v>1.3</v>
+      </c>
+      <c r="L93">
+        <v>1.8</v>
+      </c>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>10.1.1</t>
+        </is>
+      </c>
+      <c r="N93" t="inlineStr">
+        <is>
+          <t>Prosperity gap (average shortfall from a prosperity standard of $25/day)</t>
+        </is>
+      </c>
+      <c r="O93">
         <v>2015</v>
       </c>
-      <c r="J93">
-        <v>2022</v>
-      </c>
-      <c r="K93">
-        <v>1.2</v>
-      </c>
-      <c r="L93">
-        <v>0.6433333333333395</v>
-      </c>
-      <c r="M93" t="inlineStr">
-        <is>
-          <t>10.1.1</t>
-        </is>
-      </c>
-      <c r="N93" t="inlineStr">
-        <is>
-          <t>Prosperity gap (average shortfall from a prosperity standard of $25/day)</t>
-        </is>
-      </c>
-      <c r="O93">
-        <v>1.8</v>
-      </c>
       <c r="P93">
-        <v>2037</v>
-      </c>
-      <c r="Q93" t="inlineStr">
-        <is>
-          <t>future</t>
-        </is>
+        <v>1.46</v>
       </c>
     </row>
     <row r="94">
@@ -5593,25 +5308,22 @@
           <t>MDA</t>
         </is>
       </c>
-      <c r="G95">
-        <v>-0.1785714285714286</v>
-      </c>
-      <c r="H95" t="inlineStr">
+      <c r="H95">
+        <v>-0.2083333333333339</v>
+      </c>
+      <c r="I95" t="inlineStr">
         <is>
           <t>0-20</t>
         </is>
       </c>
-      <c r="I95">
-        <v>2015</v>
-      </c>
       <c r="J95">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="K95">
         <v>2.6</v>
       </c>
       <c r="L95">
-        <v>0.9295238095238165</v>
+        <v>2.5</v>
       </c>
       <c r="M95" t="inlineStr">
         <is>
@@ -5624,12 +5336,10 @@
         </is>
       </c>
       <c r="O95">
-        <v>2.5</v>
-      </c>
-      <c r="Q95" t="inlineStr">
-        <is>
-          <t>never</t>
-        </is>
+        <v>2015</v>
+      </c>
+      <c r="P95">
+        <v>2.033333333333337</v>
       </c>
     </row>
     <row r="96">
@@ -5658,10 +5368,10 @@
         </is>
       </c>
       <c r="J96">
-        <v>2012</v>
+        <v>2021</v>
       </c>
       <c r="K96">
-        <v>28.4</v>
+        <v>14.4</v>
       </c>
       <c r="M96" t="inlineStr">
         <is>
@@ -5742,10 +5452,10 @@
         </is>
       </c>
       <c r="G98">
-        <v>1.25</v>
-      </c>
-      <c r="I98">
-        <v>2016</v>
+        <v>2073</v>
+      </c>
+      <c r="H98">
+        <v>1.256613756613757</v>
       </c>
       <c r="J98">
         <v>2022</v>
@@ -5754,7 +5464,7 @@
         <v>2.9</v>
       </c>
       <c r="L98">
-        <v>1.724285714285697</v>
+        <v>3.5</v>
       </c>
       <c r="M98" t="inlineStr">
         <is>
@@ -5767,15 +5477,10 @@
         </is>
       </c>
       <c r="O98">
-        <v>3.5</v>
+        <v>2016</v>
       </c>
       <c r="P98">
-        <v>2062</v>
-      </c>
-      <c r="Q98" t="inlineStr">
-        <is>
-          <t>future</t>
-        </is>
+        <v>3.008888888888887</v>
       </c>
     </row>
     <row r="99">
@@ -5930,15 +5635,15 @@
         </is>
       </c>
       <c r="G102">
-        <v>0.4761904761904776</v>
-      </c>
-      <c r="H102" t="inlineStr">
+        <v>2036</v>
+      </c>
+      <c r="H102">
+        <v>0.7142857142857143</v>
+      </c>
+      <c r="I102" t="inlineStr">
         <is>
           <t>60-80</t>
         </is>
-      </c>
-      <c r="I102">
-        <v>2015</v>
       </c>
       <c r="J102">
         <v>2022</v>
@@ -5947,7 +5652,7 @@
         <v>0.7000000000000001</v>
       </c>
       <c r="L102">
-        <v>0.3033333333333303</v>
+        <v>0.8</v>
       </c>
       <c r="M102" t="inlineStr">
         <is>
@@ -5960,15 +5665,10 @@
         </is>
       </c>
       <c r="O102">
-        <v>0.8</v>
+        <v>2015</v>
       </c>
       <c r="P102">
-        <v>2043</v>
-      </c>
-      <c r="Q102" t="inlineStr">
-        <is>
-          <t>future</t>
-        </is>
+        <v>0.66</v>
       </c>
     </row>
     <row r="103">
@@ -6038,16 +5738,13 @@
           <t>MNE</t>
         </is>
       </c>
-      <c r="G104">
-        <v>0</v>
-      </c>
-      <c r="H104" t="inlineStr">
-        <is>
-          <t>20-40</t>
-        </is>
-      </c>
-      <c r="I104">
-        <v>2015</v>
+      <c r="H104">
+        <v>0</v>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>40-60</t>
+        </is>
       </c>
       <c r="J104">
         <v>2021</v>
@@ -6056,7 +5753,7 @@
         <v>2.8</v>
       </c>
       <c r="L104">
-        <v>1.249404761904771</v>
+        <v>2.8</v>
       </c>
       <c r="M104" t="inlineStr">
         <is>
@@ -6069,12 +5766,10 @@
         </is>
       </c>
       <c r="O104">
-        <v>2.8</v>
-      </c>
-      <c r="Q104" t="inlineStr">
-        <is>
-          <t>never</t>
-        </is>
+        <v>2015</v>
+      </c>
+      <c r="P104">
+        <v>2.41142857142857</v>
       </c>
     </row>
     <row r="105">
@@ -6103,10 +5798,10 @@
         </is>
       </c>
       <c r="G105">
-        <v>1.875</v>
-      </c>
-      <c r="I105">
-        <v>2016</v>
+        <v>2054</v>
+      </c>
+      <c r="H105">
+        <v>1.917989417989418</v>
       </c>
       <c r="J105">
         <v>2022</v>
@@ -6115,7 +5810,7 @@
         <v>2.7</v>
       </c>
       <c r="L105">
-        <v>1.799285714285724</v>
+        <v>3.6</v>
       </c>
       <c r="M105" t="inlineStr">
         <is>
@@ -6128,15 +5823,10 @@
         </is>
       </c>
       <c r="O105">
-        <v>3.6</v>
+        <v>2016</v>
       </c>
       <c r="P105">
-        <v>2048</v>
-      </c>
-      <c r="Q105" t="inlineStr">
-        <is>
-          <t>future</t>
-        </is>
+        <v>3.097777777777774</v>
       </c>
     </row>
     <row r="106">
@@ -6165,10 +5855,10 @@
         </is>
       </c>
       <c r="J106">
-        <v>2019</v>
+        <v>2022</v>
       </c>
       <c r="K106">
-        <v>25.7</v>
+        <v>24.4</v>
       </c>
       <c r="M106" t="inlineStr">
         <is>
@@ -6333,15 +6023,15 @@
         </is>
       </c>
       <c r="G110">
-        <v>0.6666666666666666</v>
-      </c>
-      <c r="H110" t="inlineStr">
+        <v>2052</v>
+      </c>
+      <c r="H110">
+        <v>0.9722222222222214</v>
+      </c>
+      <c r="I110" t="inlineStr">
         <is>
           <t>60-80</t>
         </is>
-      </c>
-      <c r="I110">
-        <v>2015</v>
       </c>
       <c r="J110">
         <v>2021</v>
@@ -6350,7 +6040,7 @@
         <v>1.2</v>
       </c>
       <c r="L110">
-        <v>0.5833333333333395</v>
+        <v>1.4</v>
       </c>
       <c r="M110" t="inlineStr">
         <is>
@@ -6363,15 +6053,10 @@
         </is>
       </c>
       <c r="O110">
-        <v>1.4</v>
+        <v>2015</v>
       </c>
       <c r="P110">
-        <v>2057</v>
-      </c>
-      <c r="Q110" t="inlineStr">
-        <is>
-          <t>future</t>
-        </is>
+        <v>1.194999999999998</v>
       </c>
     </row>
     <row r="111">
@@ -6483,11 +6168,22 @@
           <t>NGA</t>
         </is>
       </c>
+      <c r="H113">
+        <v>-0.6735554300771694</v>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>0-20</t>
+        </is>
+      </c>
       <c r="J113">
-        <v>2018</v>
+        <v>2022</v>
       </c>
       <c r="K113">
-        <v>8.699999999999999</v>
+        <v>9.800000000000001</v>
+      </c>
+      <c r="L113">
+        <v>8.700000000000001</v>
       </c>
       <c r="M113" t="inlineStr">
         <is>
@@ -6498,6 +6194,12 @@
         <is>
           <t>Prosperity gap (average shortfall from a prosperity standard of $25/day)</t>
         </is>
+      </c>
+      <c r="O113">
+        <v>2015</v>
+      </c>
+      <c r="P113">
+        <v>7.29972658920026</v>
       </c>
     </row>
     <row r="114">
@@ -6568,15 +6270,15 @@
         </is>
       </c>
       <c r="G115">
+        <v>2020</v>
+      </c>
+      <c r="H115">
         <v>0.8333333333333334</v>
       </c>
-      <c r="H115" t="inlineStr">
+      <c r="I115" t="inlineStr">
         <is>
           <t>80-100</t>
         </is>
-      </c>
-      <c r="I115">
-        <v>2015</v>
       </c>
       <c r="J115">
         <v>2021</v>
@@ -6585,7 +6287,7 @@
         <v>0.5</v>
       </c>
       <c r="L115">
-        <v>0.26</v>
+        <v>0.6000000000000001</v>
       </c>
       <c r="M115" t="inlineStr">
         <is>
@@ -6598,15 +6300,10 @@
         </is>
       </c>
       <c r="O115">
-        <v>0.6000000000000001</v>
+        <v>2015</v>
       </c>
       <c r="P115">
-        <v>2020</v>
-      </c>
-      <c r="Q115" t="inlineStr">
-        <is>
-          <t>past</t>
-        </is>
+        <v>0.48</v>
       </c>
     </row>
     <row r="116">
@@ -6634,43 +6331,38 @@
           <t>NOR</t>
         </is>
       </c>
-      <c r="G116">
-        <v>-1.428571428571429</v>
-      </c>
-      <c r="H116" t="inlineStr">
+      <c r="H116">
+        <v>-0.625</v>
+      </c>
+      <c r="I116" t="inlineStr">
         <is>
           <t>0-20</t>
         </is>
       </c>
-      <c r="I116">
+      <c r="J116">
+        <v>2023</v>
+      </c>
+      <c r="K116">
+        <v>0.6000000000000001</v>
+      </c>
+      <c r="L116">
+        <v>0.5</v>
+      </c>
+      <c r="M116" t="inlineStr">
+        <is>
+          <t>10.1.1</t>
+        </is>
+      </c>
+      <c r="N116" t="inlineStr">
+        <is>
+          <t>Prosperity gap (average shortfall from a prosperity standard of $25/day)</t>
+        </is>
+      </c>
+      <c r="O116">
         <v>2015</v>
       </c>
-      <c r="J116">
-        <v>2022</v>
-      </c>
-      <c r="K116">
-        <v>0.7000000000000001</v>
-      </c>
-      <c r="L116">
-        <v>0.2</v>
-      </c>
-      <c r="M116" t="inlineStr">
-        <is>
-          <t>10.1.1</t>
-        </is>
-      </c>
-      <c r="N116" t="inlineStr">
-        <is>
-          <t>Prosperity gap (average shortfall from a prosperity standard of $25/day)</t>
-        </is>
-      </c>
-      <c r="O116">
-        <v>0.5</v>
-      </c>
-      <c r="Q116" t="inlineStr">
-        <is>
-          <t>never</t>
-        </is>
+      <c r="P116">
+        <v>0.3700000000000001</v>
       </c>
     </row>
     <row r="117">
@@ -6825,45 +6517,40 @@
         </is>
       </c>
       <c r="G120">
-        <v>0.3125</v>
-      </c>
-      <c r="H120" t="inlineStr">
+        <v>2106</v>
+      </c>
+      <c r="H120">
+        <v>0.6878306878306878</v>
+      </c>
+      <c r="I120" t="inlineStr">
         <is>
           <t>40-60</t>
         </is>
       </c>
-      <c r="I120">
+      <c r="J120">
+        <v>2024</v>
+      </c>
+      <c r="K120">
+        <v>2.4</v>
+      </c>
+      <c r="L120">
+        <v>2.8</v>
+      </c>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>10.1.1</t>
+        </is>
+      </c>
+      <c r="N120" t="inlineStr">
+        <is>
+          <t>Prosperity gap (average shortfall from a prosperity standard of $25/day)</t>
+        </is>
+      </c>
+      <c r="O120">
         <v>2015</v>
       </c>
-      <c r="J120">
-        <v>2023</v>
-      </c>
-      <c r="K120">
-        <v>2.6</v>
-      </c>
-      <c r="L120">
-        <v>0.9195238095238165</v>
-      </c>
-      <c r="M120" t="inlineStr">
-        <is>
-          <t>10.1.1</t>
-        </is>
-      </c>
-      <c r="N120" t="inlineStr">
-        <is>
-          <t>Prosperity gap (average shortfall from a prosperity standard of $25/day)</t>
-        </is>
-      </c>
-      <c r="O120">
-        <v>2.8</v>
-      </c>
       <c r="P120">
-        <v>2172</v>
-      </c>
-      <c r="Q120" t="inlineStr">
-        <is>
-          <t>future</t>
-        </is>
+        <v>2.231428571428577</v>
       </c>
     </row>
     <row r="121">
@@ -6892,45 +6579,40 @@
         </is>
       </c>
       <c r="G121">
-        <v>0.3125</v>
-      </c>
-      <c r="H121" t="inlineStr">
+        <v>2179</v>
+      </c>
+      <c r="H121">
+        <v>0.4691358024691349</v>
+      </c>
+      <c r="I121" t="inlineStr">
         <is>
           <t>20-40</t>
         </is>
       </c>
-      <c r="I121">
+      <c r="J121">
+        <v>2024</v>
+      </c>
+      <c r="K121">
+        <v>3.6</v>
+      </c>
+      <c r="L121">
+        <v>4</v>
+      </c>
+      <c r="M121" t="inlineStr">
+        <is>
+          <t>10.1.1</t>
+        </is>
+      </c>
+      <c r="N121" t="inlineStr">
+        <is>
+          <t>Prosperity gap (average shortfall from a prosperity standard of $25/day)</t>
+        </is>
+      </c>
+      <c r="O121">
         <v>2015</v>
       </c>
-      <c r="J121">
-        <v>2023</v>
-      </c>
-      <c r="K121">
-        <v>3.8</v>
-      </c>
-      <c r="L121">
-        <v>1.619285714285703</v>
-      </c>
-      <c r="M121" t="inlineStr">
-        <is>
-          <t>10.1.1</t>
-        </is>
-      </c>
-      <c r="N121" t="inlineStr">
-        <is>
-          <t>Prosperity gap (average shortfall from a prosperity standard of $25/day)</t>
-        </is>
-      </c>
-      <c r="O121">
-        <v>4</v>
-      </c>
       <c r="P121">
-        <v>2220</v>
-      </c>
-      <c r="Q121" t="inlineStr">
-        <is>
-          <t>future</t>
-        </is>
+        <v>3.195555555555547</v>
       </c>
     </row>
     <row r="122">
@@ -6959,15 +6641,15 @@
         </is>
       </c>
       <c r="G122">
-        <v>2.142857142857142</v>
-      </c>
-      <c r="H122" t="inlineStr">
+        <v>2090</v>
+      </c>
+      <c r="H122">
+        <v>1.207126207126207</v>
+      </c>
+      <c r="I122" t="inlineStr">
         <is>
           <t>40-60</t>
         </is>
-      </c>
-      <c r="I122">
-        <v>2015</v>
       </c>
       <c r="J122">
         <v>2023</v>
@@ -6976,7 +6658,7 @@
         <v>4.4</v>
       </c>
       <c r="L122">
-        <v>3.225714285714275</v>
+        <v>5.600000000000001</v>
       </c>
       <c r="M122" t="inlineStr">
         <is>
@@ -6989,15 +6671,10 @@
         </is>
       </c>
       <c r="O122">
-        <v>5.600000000000001</v>
+        <v>2015</v>
       </c>
       <c r="P122">
-        <v>2055</v>
-      </c>
-      <c r="Q122" t="inlineStr">
-        <is>
-          <t>future</t>
-        </is>
+        <v>4.582271062271068</v>
       </c>
     </row>
     <row r="123">
@@ -7068,45 +6745,40 @@
         </is>
       </c>
       <c r="G124">
-        <v>1.285714285714286</v>
-      </c>
-      <c r="H124" t="inlineStr">
+        <v>2033</v>
+      </c>
+      <c r="H124">
+        <v>1.979166666666666</v>
+      </c>
+      <c r="I124" t="inlineStr">
         <is>
           <t>60-80</t>
         </is>
       </c>
-      <c r="I124">
+      <c r="J124">
+        <v>2023</v>
+      </c>
+      <c r="K124">
+        <v>0.9</v>
+      </c>
+      <c r="L124">
+        <v>1.4</v>
+      </c>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>10.1.1</t>
+        </is>
+      </c>
+      <c r="N124" t="inlineStr">
+        <is>
+          <t>Prosperity gap (average shortfall from a prosperity standard of $25/day)</t>
+        </is>
+      </c>
+      <c r="O124">
         <v>2015</v>
       </c>
-      <c r="J124">
-        <v>2022</v>
-      </c>
-      <c r="K124">
-        <v>1</v>
-      </c>
-      <c r="L124">
-        <v>0.5033333333333394</v>
-      </c>
-      <c r="M124" t="inlineStr">
-        <is>
-          <t>10.1.1</t>
-        </is>
-      </c>
-      <c r="N124" t="inlineStr">
-        <is>
-          <t>Prosperity gap (average shortfall from a prosperity standard of $25/day)</t>
-        </is>
-      </c>
-      <c r="O124">
-        <v>1.4</v>
-      </c>
       <c r="P124">
-        <v>2037</v>
-      </c>
-      <c r="Q124" t="inlineStr">
-        <is>
-          <t>future</t>
-        </is>
+        <v>1.135000000000001</v>
       </c>
     </row>
     <row r="125">
@@ -7135,24 +6807,24 @@
         </is>
       </c>
       <c r="G125">
-        <v>0.9285714285714286</v>
-      </c>
-      <c r="H125" t="inlineStr">
+        <v>2046</v>
+      </c>
+      <c r="H125">
+        <v>1.145833333333332</v>
+      </c>
+      <c r="I125" t="inlineStr">
         <is>
           <t>60-80</t>
         </is>
       </c>
-      <c r="I125">
-        <v>2015</v>
-      </c>
       <c r="J125">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="K125">
         <v>1.1</v>
       </c>
       <c r="L125">
-        <v>0.5033333333333394</v>
+        <v>1.4</v>
       </c>
       <c r="M125" t="inlineStr">
         <is>
@@ -7165,15 +6837,10 @@
         </is>
       </c>
       <c r="O125">
-        <v>1.4</v>
+        <v>2015</v>
       </c>
       <c r="P125">
-        <v>2045</v>
-      </c>
-      <c r="Q125" t="inlineStr">
-        <is>
-          <t>future</t>
-        </is>
+        <v>1.135000000000001</v>
       </c>
     </row>
     <row r="126">
@@ -7202,45 +6869,40 @@
         </is>
       </c>
       <c r="G126">
-        <v>0.46875</v>
-      </c>
-      <c r="H126" t="inlineStr">
-        <is>
-          <t>20-40</t>
-        </is>
-      </c>
-      <c r="I126">
+        <v>2095</v>
+      </c>
+      <c r="H126">
+        <v>0.82010582010582</v>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>40-60</t>
+        </is>
+      </c>
+      <c r="J126">
+        <v>2024</v>
+      </c>
+      <c r="K126">
+        <v>2.5</v>
+      </c>
+      <c r="L126">
+        <v>3</v>
+      </c>
+      <c r="M126" t="inlineStr">
+        <is>
+          <t>10.1.1</t>
+        </is>
+      </c>
+      <c r="N126" t="inlineStr">
+        <is>
+          <t>Prosperity gap (average shortfall from a prosperity standard of $25/day)</t>
+        </is>
+      </c>
+      <c r="O126">
         <v>2015</v>
       </c>
-      <c r="J126">
-        <v>2023</v>
-      </c>
-      <c r="K126">
-        <v>2.7</v>
-      </c>
-      <c r="L126">
-        <v>1.019523809523816</v>
-      </c>
-      <c r="M126" t="inlineStr">
-        <is>
-          <t>10.1.1</t>
-        </is>
-      </c>
-      <c r="N126" t="inlineStr">
-        <is>
-          <t>Prosperity gap (average shortfall from a prosperity standard of $25/day)</t>
-        </is>
-      </c>
-      <c r="O126">
-        <v>3</v>
-      </c>
       <c r="P126">
-        <v>2125</v>
-      </c>
-      <c r="Q126" t="inlineStr">
-        <is>
-          <t>future</t>
-        </is>
+        <v>2.402857142857143</v>
       </c>
     </row>
     <row r="127">
@@ -7268,11 +6930,8 @@
           <t>PSE</t>
         </is>
       </c>
-      <c r="G127">
-        <v>-0.1785714285714286</v>
-      </c>
-      <c r="I127">
-        <v>2016</v>
+      <c r="H127">
+        <v>-0.2040816326530615</v>
       </c>
       <c r="J127">
         <v>2023</v>
@@ -7281,7 +6940,7 @@
         <v>2.9</v>
       </c>
       <c r="L127">
-        <v>1.079523809523816</v>
+        <v>2.8</v>
       </c>
       <c r="M127" t="inlineStr">
         <is>
@@ -7294,12 +6953,10 @@
         </is>
       </c>
       <c r="O127">
-        <v>2.8</v>
-      </c>
-      <c r="Q127" t="inlineStr">
-        <is>
-          <t>never</t>
-        </is>
+        <v>2016</v>
+      </c>
+      <c r="P127">
+        <v>2.351428571428571</v>
       </c>
     </row>
     <row r="128">
@@ -7327,6 +6984,9 @@
           <t>QAT</t>
         </is>
       </c>
+      <c r="G128">
+        <v>2017</v>
+      </c>
       <c r="J128">
         <v>2017</v>
       </c>
@@ -7343,14 +7003,6 @@
           <t>Prosperity gap (average shortfall from a prosperity standard of $25/day)</t>
         </is>
       </c>
-      <c r="P128">
-        <v>2017</v>
-      </c>
-      <c r="Q128" t="inlineStr">
-        <is>
-          <t>past</t>
-        </is>
-      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -7378,45 +7030,40 @@
         </is>
       </c>
       <c r="G129">
-        <v>4.200680272108845</v>
-      </c>
-      <c r="H129" t="inlineStr">
+        <v>2029</v>
+      </c>
+      <c r="H129">
+        <v>5.311507936507937</v>
+      </c>
+      <c r="I129" t="inlineStr">
         <is>
           <t>80-100</t>
         </is>
       </c>
-      <c r="I129">
+      <c r="J129">
+        <v>2023</v>
+      </c>
+      <c r="K129">
+        <v>1.3</v>
+      </c>
+      <c r="L129">
+        <v>3.9</v>
+      </c>
+      <c r="M129" t="inlineStr">
+        <is>
+          <t>10.1.1</t>
+        </is>
+      </c>
+      <c r="N129" t="inlineStr">
+        <is>
+          <t>Prosperity gap (average shortfall from a prosperity standard of $25/day)</t>
+        </is>
+      </c>
+      <c r="O129">
         <v>2015</v>
       </c>
-      <c r="J129">
-        <v>2022</v>
-      </c>
-      <c r="K129">
-        <v>1.7</v>
-      </c>
-      <c r="L129">
-        <v>1.784285714285719</v>
-      </c>
-      <c r="M129" t="inlineStr">
-        <is>
-          <t>10.1.1</t>
-        </is>
-      </c>
-      <c r="N129" t="inlineStr">
-        <is>
-          <t>Prosperity gap (average shortfall from a prosperity standard of $25/day)</t>
-        </is>
-      </c>
-      <c r="O129">
-        <v>3.9</v>
-      </c>
       <c r="P129">
-        <v>2030</v>
-      </c>
-      <c r="Q129" t="inlineStr">
-        <is>
-          <t>future</t>
-        </is>
+        <v>3.195555555555547</v>
       </c>
     </row>
     <row r="130">
@@ -7445,42 +7092,40 @@
         </is>
       </c>
       <c r="G130">
-        <v>0</v>
-      </c>
-      <c r="H130" t="inlineStr">
+        <v>2051</v>
+      </c>
+      <c r="H130">
+        <v>0.8333333333333339</v>
+      </c>
+      <c r="I130" t="inlineStr">
         <is>
           <t>60-80</t>
         </is>
       </c>
-      <c r="I130">
+      <c r="J130">
+        <v>2023</v>
+      </c>
+      <c r="K130">
+        <v>1</v>
+      </c>
+      <c r="L130">
+        <v>1.2</v>
+      </c>
+      <c r="M130" t="inlineStr">
+        <is>
+          <t>10.1.1</t>
+        </is>
+      </c>
+      <c r="N130" t="inlineStr">
+        <is>
+          <t>Prosperity gap (average shortfall from a prosperity standard of $25/day)</t>
+        </is>
+      </c>
+      <c r="O130">
         <v>2015</v>
       </c>
-      <c r="J130">
-        <v>2021</v>
-      </c>
-      <c r="K130">
-        <v>1.2</v>
-      </c>
-      <c r="L130">
-        <v>0.5033333333333394</v>
-      </c>
-      <c r="M130" t="inlineStr">
-        <is>
-          <t>10.1.1</t>
-        </is>
-      </c>
-      <c r="N130" t="inlineStr">
-        <is>
-          <t>Prosperity gap (average shortfall from a prosperity standard of $25/day)</t>
-        </is>
-      </c>
-      <c r="O130">
-        <v>1.2</v>
-      </c>
-      <c r="Q130" t="inlineStr">
-        <is>
-          <t>never</t>
-        </is>
+      <c r="P130">
+        <v>0.9600000000000014</v>
       </c>
     </row>
     <row r="131">
@@ -7508,21 +7153,36 @@
           <t>RWA</t>
         </is>
       </c>
+      <c r="G131">
+        <v>2065</v>
+      </c>
+      <c r="H131">
+        <v>2.555328840522494</v>
+      </c>
       <c r="J131">
+        <v>2023</v>
+      </c>
+      <c r="K131">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="L131">
+        <v>13.9</v>
+      </c>
+      <c r="M131" t="inlineStr">
+        <is>
+          <t>10.1.1</t>
+        </is>
+      </c>
+      <c r="N131" t="inlineStr">
+        <is>
+          <t>Prosperity gap (average shortfall from a prosperity standard of $25/day)</t>
+        </is>
+      </c>
+      <c r="O131">
         <v>2016</v>
       </c>
-      <c r="K131">
-        <v>13.9</v>
-      </c>
-      <c r="M131" t="inlineStr">
-        <is>
-          <t>10.1.1</t>
-        </is>
-      </c>
-      <c r="N131" t="inlineStr">
-        <is>
-          <t>Prosperity gap (average shortfall from a prosperity standard of $25/day)</t>
-        </is>
+      <c r="P131">
+        <v>11.60318863615828</v>
       </c>
     </row>
     <row r="132">
@@ -7719,15 +7379,15 @@
         </is>
       </c>
       <c r="G136">
-        <v>0.46875</v>
-      </c>
-      <c r="H136" t="inlineStr">
+        <v>2203</v>
+      </c>
+      <c r="H136">
+        <v>0.4027777777777768</v>
+      </c>
+      <c r="I136" t="inlineStr">
         <is>
           <t>20-40</t>
         </is>
-      </c>
-      <c r="I136">
-        <v>2015</v>
       </c>
       <c r="J136">
         <v>2023</v>
@@ -7736,7 +7396,7 @@
         <v>3.6</v>
       </c>
       <c r="L136">
-        <v>1.544285714285717</v>
+        <v>3.9</v>
       </c>
       <c r="M136" t="inlineStr">
         <is>
@@ -7749,15 +7409,10 @@
         </is>
       </c>
       <c r="O136">
-        <v>3.9</v>
+        <v>2015</v>
       </c>
       <c r="P136">
-        <v>2149</v>
-      </c>
-      <c r="Q136" t="inlineStr">
-        <is>
-          <t>future</t>
-        </is>
+        <v>3.195555555555547</v>
       </c>
     </row>
     <row r="137">
@@ -7786,15 +7441,15 @@
         </is>
       </c>
       <c r="G137">
-        <v>7.091836734693878</v>
-      </c>
-      <c r="H137" t="inlineStr">
+        <v>2033</v>
+      </c>
+      <c r="H137">
+        <v>5.342260913689486</v>
+      </c>
+      <c r="I137" t="inlineStr">
         <is>
           <t>80-100</t>
         </is>
-      </c>
-      <c r="I137">
-        <v>2015</v>
       </c>
       <c r="J137">
         <v>2022</v>
@@ -7803,7 +7458,7 @@
         <v>2.4</v>
       </c>
       <c r="L137">
-        <v>4.117142857142826</v>
+        <v>6.100000000000001</v>
       </c>
       <c r="M137" t="inlineStr">
         <is>
@@ -7816,15 +7471,10 @@
         </is>
       </c>
       <c r="O137">
-        <v>6.100000000000001</v>
+        <v>2015</v>
       </c>
       <c r="P137">
-        <v>2028</v>
-      </c>
-      <c r="Q137" t="inlineStr">
-        <is>
-          <t>future</t>
-        </is>
+        <v>5.121428571428581</v>
       </c>
     </row>
     <row r="138">
@@ -7979,42 +7629,40 @@
         </is>
       </c>
       <c r="G141">
-        <v>-0.2380952380952367</v>
-      </c>
-      <c r="H141" t="inlineStr">
-        <is>
-          <t>0-20</t>
-        </is>
-      </c>
-      <c r="I141">
+        <v>2146</v>
+      </c>
+      <c r="H141">
+        <v>0.3125</v>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>60-80</t>
+        </is>
+      </c>
+      <c r="J141">
+        <v>2023</v>
+      </c>
+      <c r="K141">
+        <v>1.5</v>
+      </c>
+      <c r="L141">
+        <v>1.6</v>
+      </c>
+      <c r="M141" t="inlineStr">
+        <is>
+          <t>10.1.1</t>
+        </is>
+      </c>
+      <c r="N141" t="inlineStr">
+        <is>
+          <t>Prosperity gap (average shortfall from a prosperity standard of $25/day)</t>
+        </is>
+      </c>
+      <c r="O141">
         <v>2015</v>
       </c>
-      <c r="J141">
-        <v>2022</v>
-      </c>
-      <c r="K141">
-        <v>1.7</v>
-      </c>
-      <c r="L141">
-        <v>0.5766666666666607</v>
-      </c>
-      <c r="M141" t="inlineStr">
-        <is>
-          <t>10.1.1</t>
-        </is>
-      </c>
-      <c r="N141" t="inlineStr">
-        <is>
-          <t>Prosperity gap (average shortfall from a prosperity standard of $25/day)</t>
-        </is>
-      </c>
-      <c r="O141">
-        <v>1.6</v>
-      </c>
-      <c r="Q141" t="inlineStr">
-        <is>
-          <t>never</t>
-        </is>
+      <c r="P141">
+        <v>1.285</v>
       </c>
     </row>
     <row r="142">
@@ -8043,24 +7691,24 @@
         </is>
       </c>
       <c r="G142">
-        <v>1.190476190476192</v>
-      </c>
-      <c r="H142" t="inlineStr">
+        <v>2027</v>
+      </c>
+      <c r="H142">
+        <v>1.25</v>
+      </c>
+      <c r="I142" t="inlineStr">
         <is>
           <t>80-100</t>
         </is>
       </c>
-      <c r="I142">
-        <v>2015</v>
-      </c>
       <c r="J142">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="K142">
         <v>0.6000000000000001</v>
       </c>
       <c r="L142">
-        <v>0.3033333333333303</v>
+        <v>0.8</v>
       </c>
       <c r="M142" t="inlineStr">
         <is>
@@ -8073,15 +7721,10 @@
         </is>
       </c>
       <c r="O142">
-        <v>0.8</v>
+        <v>2015</v>
       </c>
       <c r="P142">
-        <v>2026</v>
-      </c>
-      <c r="Q142" t="inlineStr">
-        <is>
-          <t>future</t>
-        </is>
+        <v>0.6400000000000001</v>
       </c>
     </row>
     <row r="143">
@@ -8109,43 +7752,38 @@
           <t>SWE</t>
         </is>
       </c>
-      <c r="G143">
-        <v>-1.642857142857143</v>
-      </c>
-      <c r="H143" t="inlineStr">
+      <c r="H143">
+        <v>-0.8333333333333339</v>
+      </c>
+      <c r="I143" t="inlineStr">
         <is>
           <t>0-20</t>
         </is>
       </c>
-      <c r="I143">
+      <c r="J143">
+        <v>2023</v>
+      </c>
+      <c r="K143">
+        <v>1.1</v>
+      </c>
+      <c r="L143">
+        <v>0.9</v>
+      </c>
+      <c r="M143" t="inlineStr">
+        <is>
+          <t>10.1.1</t>
+        </is>
+      </c>
+      <c r="N143" t="inlineStr">
+        <is>
+          <t>Prosperity gap (average shortfall from a prosperity standard of $25/day)</t>
+        </is>
+      </c>
+      <c r="O143">
         <v>2015</v>
       </c>
-      <c r="J143">
-        <v>2022</v>
-      </c>
-      <c r="K143">
-        <v>1.4</v>
-      </c>
-      <c r="L143">
-        <v>0.3366666666666697</v>
-      </c>
-      <c r="M143" t="inlineStr">
-        <is>
-          <t>10.1.1</t>
-        </is>
-      </c>
-      <c r="N143" t="inlineStr">
-        <is>
-          <t>Prosperity gap (average shortfall from a prosperity standard of $25/day)</t>
-        </is>
-      </c>
-      <c r="O143">
-        <v>0.9</v>
-      </c>
-      <c r="Q143" t="inlineStr">
-        <is>
-          <t>never</t>
-        </is>
+      <c r="P143">
+        <v>0.7400000000000001</v>
       </c>
     </row>
     <row r="144">
@@ -8342,15 +7980,15 @@
         </is>
       </c>
       <c r="G148">
-        <v>2.625866554187823</v>
-      </c>
-      <c r="H148" t="inlineStr">
+        <v>2048</v>
+      </c>
+      <c r="H148">
+        <v>4.028694432291135</v>
+      </c>
+      <c r="I148" t="inlineStr">
         <is>
           <t>80-100</t>
         </is>
-      </c>
-      <c r="I148">
-        <v>2015</v>
       </c>
       <c r="J148">
         <v>2021</v>
@@ -8359,7 +7997,7 @@
         <v>8.6</v>
       </c>
       <c r="L148">
-        <v>7.317504071886076</v>
+        <v>16</v>
       </c>
       <c r="M148" t="inlineStr">
         <is>
@@ -8372,15 +8010,10 @@
         </is>
       </c>
       <c r="O148">
-        <v>16.1</v>
+        <v>2015</v>
       </c>
       <c r="P148">
-        <v>2065</v>
-      </c>
-      <c r="Q148" t="inlineStr">
-        <is>
-          <t>future</t>
-        </is>
+        <v>13.67596527479389</v>
       </c>
     </row>
     <row r="149">
@@ -8409,15 +8042,15 @@
         </is>
       </c>
       <c r="G149">
-        <v>0.5357142857142847</v>
-      </c>
-      <c r="H149" t="inlineStr">
+        <v>2090</v>
+      </c>
+      <c r="H149">
+        <v>0.7083333333333339</v>
+      </c>
+      <c r="I149" t="inlineStr">
         <is>
           <t>40-60</t>
         </is>
-      </c>
-      <c r="I149">
-        <v>2015</v>
       </c>
       <c r="J149">
         <v>2023</v>
@@ -8426,7 +8059,7 @@
         <v>1.9</v>
       </c>
       <c r="L149">
-        <v>0.6823809523809542</v>
+        <v>2.2</v>
       </c>
       <c r="M149" t="inlineStr">
         <is>
@@ -8439,15 +8072,10 @@
         </is>
       </c>
       <c r="O149">
-        <v>2.2</v>
+        <v>2015</v>
       </c>
       <c r="P149">
-        <v>2092</v>
-      </c>
-      <c r="Q149" t="inlineStr">
-        <is>
-          <t>future</t>
-        </is>
+        <v>1.783333333333337</v>
       </c>
     </row>
     <row r="150">
@@ -8475,21 +8103,41 @@
           <t>TJK</t>
         </is>
       </c>
+      <c r="G150">
+        <v>2086</v>
+      </c>
+      <c r="H150">
+        <v>1.305805305805305</v>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>40-60</t>
+        </is>
+      </c>
       <c r="J150">
+        <v>2024</v>
+      </c>
+      <c r="K150">
+        <v>4.4</v>
+      </c>
+      <c r="L150">
+        <v>5.9</v>
+      </c>
+      <c r="M150" t="inlineStr">
+        <is>
+          <t>10.1.1</t>
+        </is>
+      </c>
+      <c r="N150" t="inlineStr">
+        <is>
+          <t>Prosperity gap (average shortfall from a prosperity standard of $25/day)</t>
+        </is>
+      </c>
+      <c r="O150">
         <v>2015</v>
       </c>
-      <c r="K150">
-        <v>5.9</v>
-      </c>
-      <c r="M150" t="inlineStr">
-        <is>
-          <t>10.1.1</t>
-        </is>
-      </c>
-      <c r="N150" t="inlineStr">
-        <is>
-          <t>Prosperity gap (average shortfall from a prosperity standard of $25/day)</t>
-        </is>
+      <c r="P150">
+        <v>4.712087912087902</v>
       </c>
     </row>
     <row r="151">
@@ -8563,7 +8211,7 @@
         <v>2014</v>
       </c>
       <c r="K152">
-        <v>9.5</v>
+        <v>9.4</v>
       </c>
       <c r="M152" t="inlineStr">
         <is>
@@ -8602,15 +8250,15 @@
         </is>
       </c>
       <c r="G153">
-        <v>3.125</v>
-      </c>
-      <c r="H153" t="inlineStr">
+        <v>2043</v>
+      </c>
+      <c r="H153">
+        <v>2.868446368446369</v>
+      </c>
+      <c r="I153" t="inlineStr">
         <is>
           <t>80-100</t>
         </is>
-      </c>
-      <c r="I153">
-        <v>2015</v>
       </c>
       <c r="J153">
         <v>2021</v>
@@ -8619,7 +8267,7 @@
         <v>2.8</v>
       </c>
       <c r="L153">
-        <v>2.39500000000001</v>
+        <v>4.3</v>
       </c>
       <c r="M153" t="inlineStr">
         <is>
@@ -8632,15 +8280,10 @@
         </is>
       </c>
       <c r="O153">
-        <v>4.3</v>
+        <v>2015</v>
       </c>
       <c r="P153">
-        <v>2037</v>
-      </c>
-      <c r="Q153" t="inlineStr">
-        <is>
-          <t>future</t>
-        </is>
+        <v>3.701818181818187</v>
       </c>
     </row>
     <row r="154">
@@ -8711,15 +8354,15 @@
         </is>
       </c>
       <c r="G155">
-        <v>0.2083333333333333</v>
-      </c>
-      <c r="H155" t="inlineStr">
+        <v>2230</v>
+      </c>
+      <c r="H155">
+        <v>0.2777777777777786</v>
+      </c>
+      <c r="I155" t="inlineStr">
         <is>
           <t>40-60</t>
         </is>
-      </c>
-      <c r="I155">
-        <v>2015</v>
       </c>
       <c r="J155">
         <v>2021</v>
@@ -8728,7 +8371,7 @@
         <v>2.5</v>
       </c>
       <c r="L155">
-        <v>1.139523809523816</v>
+        <v>2.6</v>
       </c>
       <c r="M155" t="inlineStr">
         <is>
@@ -8741,15 +8384,10 @@
         </is>
       </c>
       <c r="O155">
-        <v>2.6</v>
+        <v>2015</v>
       </c>
       <c r="P155">
-        <v>2239</v>
-      </c>
-      <c r="Q155" t="inlineStr">
-        <is>
-          <t>future</t>
-        </is>
+        <v>2.240000000000003</v>
       </c>
     </row>
     <row r="156">
@@ -8778,15 +8416,15 @@
         </is>
       </c>
       <c r="G156">
-        <v>1.462585034013606</v>
-      </c>
-      <c r="H156" t="inlineStr">
+        <v>2047</v>
+      </c>
+      <c r="H156">
+        <v>1.80952380952381</v>
+      </c>
+      <c r="I156" t="inlineStr">
         <is>
           <t>40-60</t>
         </is>
-      </c>
-      <c r="I156">
-        <v>2015</v>
       </c>
       <c r="J156">
         <v>2022</v>
@@ -8795,7 +8433,7 @@
         <v>1.8</v>
       </c>
       <c r="L156">
-        <v>0.9295238095238165</v>
+        <v>2.5</v>
       </c>
       <c r="M156" t="inlineStr">
         <is>
@@ -8808,15 +8446,10 @@
         </is>
       </c>
       <c r="O156">
-        <v>2.5</v>
+        <v>2015</v>
       </c>
       <c r="P156">
-        <v>2046</v>
-      </c>
-      <c r="Q156" t="inlineStr">
-        <is>
-          <t>future</t>
-        </is>
+        <v>2.083333333333337</v>
       </c>
     </row>
     <row r="157">
@@ -8971,15 +8604,15 @@
         </is>
       </c>
       <c r="G160">
-        <v>1.357142857142858</v>
-      </c>
-      <c r="H160" t="inlineStr">
+        <v>2053</v>
+      </c>
+      <c r="H160">
+        <v>1.61904761904762</v>
+      </c>
+      <c r="I160" t="inlineStr">
         <is>
           <t>40-60</t>
         </is>
-      </c>
-      <c r="I160">
-        <v>2015</v>
       </c>
       <c r="J160">
         <v>2020</v>
@@ -8988,7 +8621,7 @@
         <v>2.2</v>
       </c>
       <c r="L160">
-        <v>1.386904761904771</v>
+        <v>2.7</v>
       </c>
       <c r="M160" t="inlineStr">
         <is>
@@ -9001,15 +8634,10 @@
         </is>
       </c>
       <c r="O160">
-        <v>2.7</v>
+        <v>2015</v>
       </c>
       <c r="P160">
-        <v>2050</v>
-      </c>
-      <c r="Q160" t="inlineStr">
-        <is>
-          <t>future</t>
-        </is>
+        <v>2.385714285714288</v>
       </c>
     </row>
     <row r="161">
@@ -9037,43 +8665,38 @@
           <t>URY</t>
         </is>
       </c>
-      <c r="G161">
-        <v>-0.25</v>
-      </c>
-      <c r="H161" t="inlineStr">
-        <is>
-          <t>0-20</t>
-        </is>
-      </c>
-      <c r="I161">
+      <c r="H161">
+        <v>0</v>
+      </c>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>60-80</t>
+        </is>
+      </c>
+      <c r="J161">
+        <v>2024</v>
+      </c>
+      <c r="K161">
+        <v>1.4</v>
+      </c>
+      <c r="L161">
+        <v>1.4</v>
+      </c>
+      <c r="M161" t="inlineStr">
+        <is>
+          <t>10.1.1</t>
+        </is>
+      </c>
+      <c r="N161" t="inlineStr">
+        <is>
+          <t>Prosperity gap (average shortfall from a prosperity standard of $25/day)</t>
+        </is>
+      </c>
+      <c r="O161">
         <v>2015</v>
       </c>
-      <c r="J161">
-        <v>2023</v>
-      </c>
-      <c r="K161">
-        <v>1.5</v>
-      </c>
-      <c r="L161">
-        <v>0.4233333333333394</v>
-      </c>
-      <c r="M161" t="inlineStr">
-        <is>
-          <t>10.1.1</t>
-        </is>
-      </c>
-      <c r="N161" t="inlineStr">
-        <is>
-          <t>Prosperity gap (average shortfall from a prosperity standard of $25/day)</t>
-        </is>
-      </c>
-      <c r="O161">
-        <v>1.4</v>
-      </c>
-      <c r="Q161" t="inlineStr">
-        <is>
-          <t>never</t>
-        </is>
+      <c r="P161">
+        <v>1.105000000000002</v>
       </c>
     </row>
     <row r="162">
@@ -9102,15 +8725,15 @@
         </is>
       </c>
       <c r="G162">
-        <v>0.25</v>
-      </c>
-      <c r="H162" t="inlineStr">
+        <v>2138</v>
+      </c>
+      <c r="H162">
+        <v>0.3125</v>
+      </c>
+      <c r="I162" t="inlineStr">
         <is>
           <t>60-80</t>
         </is>
-      </c>
-      <c r="I162">
-        <v>2015</v>
       </c>
       <c r="J162">
         <v>2023</v>
@@ -9119,7 +8742,7 @@
         <v>1.4</v>
       </c>
       <c r="L162">
-        <v>0.4633333333333394</v>
+        <v>1.5</v>
       </c>
       <c r="M162" t="inlineStr">
         <is>
@@ -9132,15 +8755,10 @@
         </is>
       </c>
       <c r="O162">
-        <v>1.5</v>
+        <v>2015</v>
       </c>
       <c r="P162">
-        <v>2136</v>
-      </c>
-      <c r="Q162" t="inlineStr">
-        <is>
-          <t>future</t>
-        </is>
+        <v>1.209999999999998</v>
       </c>
     </row>
     <row r="163">
@@ -9169,10 +8787,10 @@
         </is>
       </c>
       <c r="J163">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="K163">
-        <v>3.2</v>
+        <v>2.8</v>
       </c>
       <c r="M163" t="inlineStr">
         <is>
@@ -9253,10 +8871,10 @@
         </is>
       </c>
       <c r="G165">
-        <v>0.8333333333333334</v>
-      </c>
-      <c r="I165">
-        <v>2016</v>
+        <v>2085</v>
+      </c>
+      <c r="H165">
+        <v>0.9523809523809513</v>
       </c>
       <c r="J165">
         <v>2022</v>
@@ -9265,7 +8883,7 @@
         <v>2.6</v>
       </c>
       <c r="L165">
-        <v>1.374404761904771</v>
+        <v>3</v>
       </c>
       <c r="M165" t="inlineStr">
         <is>
@@ -9278,15 +8896,10 @@
         </is>
       </c>
       <c r="O165">
-        <v>3</v>
+        <v>2016</v>
       </c>
       <c r="P165">
-        <v>2078</v>
-      </c>
-      <c r="Q165" t="inlineStr">
-        <is>
-          <t>future</t>
-        </is>
+        <v>2.582857142857145</v>
       </c>
     </row>
     <row r="166">
@@ -9398,43 +9011,38 @@
           <t>XKX</t>
         </is>
       </c>
-      <c r="G168">
-        <v>-10.26532821198584</v>
-      </c>
-      <c r="H168" t="inlineStr">
+      <c r="H168">
+        <v>-3.738844108370867</v>
+      </c>
+      <c r="I168" t="inlineStr">
         <is>
           <t>0-20</t>
         </is>
       </c>
-      <c r="I168">
+      <c r="J168">
+        <v>2022</v>
+      </c>
+      <c r="K168">
+        <v>7.5</v>
+      </c>
+      <c r="L168">
+        <v>3.9</v>
+      </c>
+      <c r="M168" t="inlineStr">
+        <is>
+          <t>10.1.1</t>
+        </is>
+      </c>
+      <c r="N168" t="inlineStr">
+        <is>
+          <t>Prosperity gap (average shortfall from a prosperity standard of $25/day)</t>
+        </is>
+      </c>
+      <c r="O168">
         <v>2015</v>
       </c>
-      <c r="J168">
-        <v>2021</v>
-      </c>
-      <c r="K168">
-        <v>11.9</v>
-      </c>
-      <c r="L168">
-        <v>2.044999999999978</v>
-      </c>
-      <c r="M168" t="inlineStr">
-        <is>
-          <t>10.1.1</t>
-        </is>
-      </c>
-      <c r="N168" t="inlineStr">
-        <is>
-          <t>Prosperity gap (average shortfall from a prosperity standard of $25/day)</t>
-        </is>
-      </c>
-      <c r="O168">
-        <v>3.9</v>
-      </c>
-      <c r="Q168" t="inlineStr">
-        <is>
-          <t>never</t>
-        </is>
+      <c r="P168">
+        <v>3.275555555555548</v>
       </c>
     </row>
     <row r="169">
@@ -9546,16 +9154,13 @@
           <t>ZMB</t>
         </is>
       </c>
-      <c r="G171">
-        <v>0</v>
-      </c>
-      <c r="H171" t="inlineStr">
-        <is>
-          <t>40-60</t>
-        </is>
-      </c>
-      <c r="I171">
-        <v>2015</v>
+      <c r="H171">
+        <v>0</v>
+      </c>
+      <c r="I171" t="inlineStr">
+        <is>
+          <t>20-40</t>
+        </is>
       </c>
       <c r="J171">
         <v>2022</v>
@@ -9564,7 +9169,7 @@
         <v>22.9</v>
       </c>
       <c r="L171">
-        <v>6.033451987179585</v>
+        <v>22.9</v>
       </c>
       <c r="M171" t="inlineStr">
         <is>
@@ -9577,12 +9182,10 @@
         </is>
       </c>
       <c r="O171">
-        <v>22.9</v>
-      </c>
-      <c r="Q171" t="inlineStr">
-        <is>
-          <t>never</t>
-        </is>
+        <v>2015</v>
+      </c>
+      <c r="P171">
+        <v>18.70359243026799</v>
       </c>
     </row>
     <row r="172">
